--- a/003_NRC_MORPHOGENETIC/gridConvergence_D01_V1.xlsx
+++ b/003_NRC_MORPHOGENETIC/gridConvergence_D01_V1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\forsythp\Documents\Projects\IPW-3\IPW3-main\004_NRC_MORPHOGENETIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkzayni/Desktop/UNIVERSITY/POST_PROCESS/postProcessingData/003_NRC_MORPHOGENETIC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2FC6370-DE8A-44AD-940E-8E77DB0FF848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77551EE5-AC55-AE43-A4FD-DEF45EA0D34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="850" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="29040" windowHeight="15720" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUCTIONS" sheetId="1" r:id="rId1"/>
@@ -34,9 +34,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -451,7 +448,7 @@
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -682,7 +679,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -797,9 +794,6 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -810,9 +804,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -826,16 +817,16 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -871,7 +862,7 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1304,386 +1295,386 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E78"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="96.375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.75" customWidth="1"/>
-    <col min="5" max="5" width="16.375" customWidth="1"/>
+    <col min="1" max="1" width="96.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75">
+    <row r="1" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15.75">
+    <row r="2" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="51"/>
     </row>
-    <row r="3" spans="1:1" ht="15.75">
+    <row r="3" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="51"/>
     </row>
-    <row r="4" spans="1:1" ht="15.75">
+    <row r="4" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="51" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.75">
+    <row r="5" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="51"/>
     </row>
-    <row r="6" spans="1:1" ht="21">
+    <row r="6" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="21">
+    <row r="7" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="21">
+    <row r="8" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="21">
+    <row r="9" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="21">
+    <row r="10" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="21">
+    <row r="11" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="21">
+    <row r="12" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15.75">
+    <row r="13" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="52" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="15.75">
+    <row r="14" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="52"/>
     </row>
-    <row r="15" spans="1:1" ht="21">
+    <row r="15" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="21">
+    <row r="16" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="21">
+    <row r="17" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="21">
+    <row r="18" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="21">
+    <row r="19" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75">
+    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="51" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75">
+    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="51"/>
     </row>
-    <row r="22" spans="1:5" ht="21">
+    <row r="22" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="21">
+    <row r="23" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="21">
+    <row r="24" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="21">
+    <row r="25" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="21">
+    <row r="26" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="21">
+    <row r="27" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E27" s="4"/>
     </row>
-    <row r="28" spans="1:5" ht="21">
+    <row r="28" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="21">
+    <row r="29" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="21">
+    <row r="30" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E30" s="4"/>
     </row>
-    <row r="31" spans="1:5" ht="21">
+    <row r="31" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E31" s="4"/>
     </row>
-    <row r="32" spans="1:5" ht="15.75">
+    <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="51" t="s">
         <v>22</v>
       </c>
       <c r="E32" s="4"/>
     </row>
-    <row r="33" spans="1:5" ht="15.75">
+    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="51"/>
       <c r="E33" s="4"/>
     </row>
-    <row r="34" spans="1:5" ht="21">
+    <row r="34" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E34" s="4"/>
     </row>
-    <row r="35" spans="1:5" ht="21">
+    <row r="35" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="4"/>
     </row>
-    <row r="36" spans="1:5" ht="21">
+    <row r="36" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E36" s="4"/>
     </row>
-    <row r="37" spans="1:5" ht="21">
+    <row r="37" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E37" s="4"/>
     </row>
-    <row r="38" spans="1:5" ht="21">
+    <row r="38" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E38" s="4"/>
     </row>
-    <row r="39" spans="1:5" ht="21">
+    <row r="39" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="21">
+    <row r="40" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E40" s="4"/>
     </row>
-    <row r="41" spans="1:5" ht="21">
+    <row r="41" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E41" s="4"/>
     </row>
-    <row r="42" spans="1:5" ht="21">
+    <row r="42" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E42" s="4"/>
     </row>
-    <row r="43" spans="1:5" ht="21">
+    <row r="43" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:5" ht="15.75">
+    <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="51" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15.75">
+    <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="51"/>
       <c r="E45" s="4"/>
     </row>
-    <row r="46" spans="1:5" ht="21">
+    <row r="46" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E46" s="4"/>
     </row>
-    <row r="47" spans="1:5" ht="21">
+    <row r="47" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E47" s="4"/>
     </row>
-    <row r="48" spans="1:5" ht="21">
+    <row r="48" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E48" s="4"/>
     </row>
-    <row r="49" spans="1:5" ht="21">
+    <row r="49" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>29</v>
       </c>
       <c r="E49" s="4"/>
     </row>
-    <row r="50" spans="1:5" ht="21">
+    <row r="50" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E50" s="4"/>
     </row>
-    <row r="51" spans="1:5" ht="21">
+    <row r="51" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="E51" s="4"/>
     </row>
-    <row r="52" spans="1:5" ht="21">
+    <row r="52" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E52" s="4"/>
     </row>
-    <row r="53" spans="1:5" ht="21">
+    <row r="53" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>33</v>
       </c>
       <c r="E53" s="4"/>
     </row>
-    <row r="54" spans="1:5" ht="21">
+    <row r="54" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E54" s="4"/>
     </row>
-    <row r="55" spans="1:5" ht="21">
+    <row r="55" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E55" s="4"/>
     </row>
-    <row r="56" spans="1:5" ht="15.75">
+    <row r="56" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="51" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.75">
+    <row r="57" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="51"/>
       <c r="E57" s="4"/>
     </row>
-    <row r="58" spans="1:5" ht="21">
+    <row r="58" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>36</v>
       </c>
       <c r="E58" s="4"/>
     </row>
-    <row r="59" spans="1:5" ht="20.25">
+    <row r="59" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
         <v>37</v>
       </c>
       <c r="E59" s="4"/>
     </row>
-    <row r="60" spans="1:5" ht="21">
+    <row r="60" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>68</v>
       </c>
       <c r="E60" s="4"/>
     </row>
-    <row r="61" spans="1:5" ht="21">
+    <row r="61" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E61" s="4"/>
     </row>
-    <row r="62" spans="1:5" ht="21">
+    <row r="62" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E62" s="4"/>
     </row>
-    <row r="63" spans="1:5" ht="21">
+    <row r="63" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E63" s="4"/>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E64" s="4"/>
     </row>
-    <row r="65" spans="5:5">
+    <row r="65" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E65" s="4"/>
     </row>
-    <row r="66" spans="5:5">
+    <row r="66" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E66" s="4"/>
     </row>
-    <row r="68" spans="5:5">
+    <row r="68" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E68" s="4"/>
     </row>
-    <row r="69" spans="5:5">
+    <row r="69" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E69" s="4"/>
     </row>
-    <row r="70" spans="5:5">
+    <row r="70" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E70" s="4"/>
     </row>
-    <row r="71" spans="5:5">
+    <row r="71" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E71" s="4"/>
     </row>
-    <row r="72" spans="5:5">
+    <row r="72" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E72" s="4"/>
     </row>
-    <row r="73" spans="5:5">
+    <row r="73" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E73" s="4"/>
     </row>
-    <row r="74" spans="5:5">
+    <row r="74" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E74" s="4"/>
     </row>
-    <row r="75" spans="5:5">
+    <row r="75" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E75" s="4"/>
     </row>
-    <row r="76" spans="5:5">
+    <row r="76" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E76" s="4"/>
     </row>
-    <row r="77" spans="5:5">
+    <row r="77" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E77" s="4"/>
     </row>
-    <row r="78" spans="5:5">
+    <row r="78" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E78" s="4"/>
     </row>
   </sheetData>
@@ -1704,79 +1695,79 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{396D4AB3-D735-C84A-BDAA-B734A45CA873}">
   <dimension ref="A1:L46"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="26.25">
-      <c r="A1" s="75" t="s">
+    <row r="1" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A1" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-    </row>
-    <row r="2" spans="1:12" s="6" customFormat="1" ht="59.1" customHeight="1">
-      <c r="A2" s="71" t="s">
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+    </row>
+    <row r="2" spans="1:12" s="6" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="73"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="71"/>
       <c r="J2" s="39"/>
       <c r="K2" s="39"/>
       <c r="L2" s="39"/>
     </row>
-    <row r="3" spans="1:12" ht="26.25">
-      <c r="A3" s="67" t="s">
+    <row r="3" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A3" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="69"/>
-    </row>
-    <row r="4" spans="1:12" ht="26.25">
-      <c r="A4" s="59" t="s">
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="67"/>
+    </row>
+    <row r="4" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A4" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="59"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="60" t="s">
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="61"/>
-      <c r="I4" s="62"/>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="H4" s="59"/>
+      <c r="I4" s="60"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
         <v>50</v>
       </c>
@@ -1805,7 +1796,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="29">
         <v>1</v>
       </c>
@@ -1828,7 +1819,7 @@
         <v>9.6199999999999992</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="29">
         <v>2</v>
       </c>
@@ -1851,7 +1842,7 @@
         <v>13.36</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="29">
         <v>3</v>
       </c>
@@ -1874,7 +1865,7 @@
         <v>16.72</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="29">
         <v>4</v>
       </c>
@@ -1897,7 +1888,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="29">
         <v>5</v>
       </c>
@@ -1920,7 +1911,7 @@
         <v>23.28</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="29">
         <v>6</v>
       </c>
@@ -1943,7 +1934,7 @@
         <v>26.64</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="29">
         <v>7</v>
       </c>
@@ -1966,7 +1957,7 @@
         <v>30.38</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="19"/>
       <c r="B13" s="11"/>
       <c r="C13" s="19"/>
@@ -1977,37 +1968,37 @@
       <c r="H13" s="11"/>
       <c r="I13" s="19"/>
     </row>
-    <row r="14" spans="1:12" ht="26.25">
-      <c r="A14" s="67" t="s">
+    <row r="14" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A14" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="68"/>
-      <c r="C14" s="68"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="68"/>
-      <c r="H14" s="68"/>
-      <c r="I14" s="69"/>
-    </row>
-    <row r="15" spans="1:12" ht="26.25">
-      <c r="A15" s="59" t="s">
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="67"/>
+    </row>
+    <row r="15" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A15" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59" t="s">
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="59"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="60" t="s">
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="H15" s="61"/>
-      <c r="I15" s="62"/>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="H15" s="59"/>
+      <c r="I15" s="60"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="19" t="s">
         <v>50</v>
       </c>
@@ -2036,7 +2027,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="29">
         <v>1</v>
       </c>
@@ -2059,7 +2050,7 @@
         <v>9.6199999999999992</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="29">
         <v>2</v>
       </c>
@@ -2082,7 +2073,7 @@
         <v>13.36</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="29">
         <v>3</v>
       </c>
@@ -2105,7 +2096,7 @@
         <v>16.72</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="29">
         <v>4</v>
       </c>
@@ -2128,7 +2119,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="29">
         <v>5</v>
       </c>
@@ -2151,7 +2142,7 @@
         <v>23.28</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="29">
         <v>6</v>
       </c>
@@ -2174,7 +2165,7 @@
         <v>26.64</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="29">
         <v>7</v>
       </c>
@@ -2197,7 +2188,7 @@
         <v>30.38</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="19"/>
       <c r="B24" s="11"/>
       <c r="C24" s="19"/>
@@ -2208,37 +2199,37 @@
       <c r="H24" s="11"/>
       <c r="I24" s="19"/>
     </row>
-    <row r="25" spans="1:9" ht="26.25">
-      <c r="A25" s="67" t="s">
+    <row r="25" spans="1:9" ht="27" x14ac:dyDescent="0.2">
+      <c r="A25" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="68"/>
-      <c r="C25" s="68"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="68"/>
-      <c r="H25" s="68"/>
-      <c r="I25" s="69"/>
-    </row>
-    <row r="26" spans="1:9" ht="26.25">
-      <c r="A26" s="59" t="s">
+      <c r="B25" s="66"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="66"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="66"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="67"/>
+    </row>
+    <row r="26" spans="1:9" ht="27" x14ac:dyDescent="0.2">
+      <c r="A26" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="59"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59" t="s">
+      <c r="B26" s="57"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="60" t="s">
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="H26" s="61"/>
-      <c r="I26" s="62"/>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="H26" s="59"/>
+      <c r="I26" s="60"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="19" t="s">
         <v>50</v>
       </c>
@@ -2267,7 +2258,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="29">
         <v>1</v>
       </c>
@@ -2290,7 +2281,7 @@
         <v>9.6199999999999992</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="29">
         <v>2</v>
       </c>
@@ -2313,7 +2304,7 @@
         <v>13.36</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="29">
         <v>3</v>
       </c>
@@ -2336,7 +2327,7 @@
         <v>16.72</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="29">
         <v>4</v>
       </c>
@@ -2359,7 +2350,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="29">
         <v>5</v>
       </c>
@@ -2382,7 +2373,7 @@
         <v>23.28</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="29">
         <v>6</v>
       </c>
@@ -2405,7 +2396,7 @@
         <v>26.64</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="29">
         <v>7</v>
       </c>
@@ -2428,7 +2419,7 @@
         <v>30.38</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="19"/>
       <c r="B35" s="11"/>
       <c r="C35" s="19"/>
@@ -2439,37 +2430,37 @@
       <c r="H35" s="11"/>
       <c r="I35" s="19"/>
     </row>
-    <row r="36" spans="1:9" ht="26.25">
-      <c r="A36" s="67" t="s">
+    <row r="36" spans="1:9" ht="27" x14ac:dyDescent="0.2">
+      <c r="A36" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="68"/>
-      <c r="C36" s="68"/>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="68"/>
-      <c r="H36" s="68"/>
-      <c r="I36" s="69"/>
-    </row>
-    <row r="37" spans="1:9" ht="26.25">
-      <c r="A37" s="59" t="s">
+      <c r="B36" s="66"/>
+      <c r="C36" s="66"/>
+      <c r="D36" s="66"/>
+      <c r="E36" s="66"/>
+      <c r="F36" s="66"/>
+      <c r="G36" s="66"/>
+      <c r="H36" s="66"/>
+      <c r="I36" s="67"/>
+    </row>
+    <row r="37" spans="1:9" ht="27" x14ac:dyDescent="0.2">
+      <c r="A37" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="59"/>
-      <c r="C37" s="59"/>
-      <c r="D37" s="59" t="s">
+      <c r="B37" s="57"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="E37" s="59"/>
-      <c r="F37" s="59"/>
-      <c r="G37" s="60" t="s">
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="H37" s="61"/>
-      <c r="I37" s="62"/>
-    </row>
-    <row r="38" spans="1:9">
+      <c r="H37" s="59"/>
+      <c r="I37" s="60"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="19" t="s">
         <v>50</v>
       </c>
@@ -2498,7 +2489,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="29">
         <v>1</v>
       </c>
@@ -2521,7 +2512,7 @@
         <v>9.6199999999999992</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="29">
         <v>2</v>
       </c>
@@ -2544,7 +2535,7 @@
         <v>13.36</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="29">
         <v>3</v>
       </c>
@@ -2567,7 +2558,7 @@
         <v>16.72</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="29">
         <v>4</v>
       </c>
@@ -2590,7 +2581,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="29">
         <v>5</v>
       </c>
@@ -2613,7 +2604,7 @@
         <v>23.28</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="29">
         <v>6</v>
       </c>
@@ -2636,7 +2627,7 @@
         <v>26.64</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="29">
         <v>7</v>
       </c>
@@ -2659,7 +2650,7 @@
         <v>30.38</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="19"/>
       <c r="B46" s="11"/>
       <c r="C46" s="19"/>
@@ -2698,23 +2689,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AMJ73"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="58" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="8.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="11.125" style="6"/>
+    <col min="4" max="4" width="13.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="11.1640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1024" ht="26.25">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
+      <c r="A1" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-    </row>
-    <row r="2" spans="1:1024">
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+    </row>
+    <row r="2" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
         <v>40</v>
       </c>
@@ -2732,7 +2723,7 @@
       <c r="Q2" s="16"/>
       <c r="R2" s="16"/>
     </row>
-    <row r="3" spans="1:1024">
+    <row r="3" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -3757,13 +3748,13 @@
       <c r="AMI3" s="10"/>
       <c r="AMJ3" s="10"/>
     </row>
-    <row r="4" spans="1:1024" ht="26.25">
-      <c r="A4" s="53" t="s">
+    <row r="4" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
+      <c r="A4" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="J4" s="7"/>
@@ -3774,7 +3765,7 @@
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
     </row>
-    <row r="5" spans="1:1024">
+    <row r="5" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>40</v>
       </c>
@@ -3797,19 +3788,15 @@
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
     </row>
-    <row r="6" spans="1:1024">
+    <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
         <v>1</v>
       </c>
-      <c r="B6" s="45">
-        <v>4.3153999999999998E-2</v>
-      </c>
-      <c r="C6" s="45">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11">
         <v>2.6550000000000001E-2</v>
       </c>
-      <c r="D6" s="45">
-        <v>0.38912000000000002</v>
-      </c>
+      <c r="D6" s="11"/>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
@@ -4831,13 +4818,13 @@
       <c r="AMI6" s="10"/>
       <c r="AMJ6" s="10"/>
     </row>
-    <row r="7" spans="1:1024" ht="26.25">
-      <c r="A7" s="53" t="s">
+    <row r="7" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
+      <c r="A7" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="J7" s="7"/>
@@ -4848,7 +4835,7 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
     </row>
-    <row r="8" spans="1:1024">
+    <row r="8" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>40</v>
       </c>
@@ -4871,19 +4858,15 @@
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
     </row>
-    <row r="9" spans="1:1024">
+    <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>1</v>
       </c>
-      <c r="B9" s="35">
-        <v>4.2526000000000001E-2</v>
-      </c>
+      <c r="B9" s="35"/>
       <c r="C9" s="35">
         <v>2.683E-2</v>
       </c>
-      <c r="D9" s="35">
-        <v>0.38844000000000001</v>
-      </c>
+      <c r="D9" s="35"/>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
       <c r="G9" s="10"/>
@@ -5905,13 +5888,13 @@
       <c r="AMI9" s="10"/>
       <c r="AMJ9" s="10"/>
     </row>
-    <row r="10" spans="1:1024" ht="26.25">
-      <c r="A10" s="53" t="s">
+    <row r="10" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
+      <c r="A10" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
       <c r="G10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
@@ -5921,7 +5904,7 @@
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
     </row>
-    <row r="11" spans="1:1024">
+    <row r="11" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
         <v>40</v>
       </c>
@@ -5942,19 +5925,15 @@
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
     </row>
-    <row r="12" spans="1:1024">
+    <row r="12" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
         <v>1</v>
       </c>
-      <c r="B12" s="11">
-        <v>4.2179000000000001E-2</v>
-      </c>
+      <c r="B12" s="11"/>
       <c r="C12" s="11">
         <v>2.7140000000000001E-2</v>
       </c>
-      <c r="D12" s="11">
-        <v>0.38923000000000002</v>
-      </c>
+      <c r="D12" s="11"/>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
@@ -6976,7 +6955,7 @@
       <c r="AMI12" s="10"/>
       <c r="AMJ12" s="10"/>
     </row>
-    <row r="13" spans="1:1024">
+    <row r="13" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
@@ -6985,13 +6964,13 @@
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
     </row>
-    <row r="14" spans="1:1024" ht="26.25">
-      <c r="A14" s="54" t="s">
+    <row r="14" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
+      <c r="A14" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
@@ -7000,7 +6979,7 @@
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
     </row>
-    <row r="15" spans="1:1024">
+    <row r="15" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
@@ -7009,7 +6988,7 @@
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
     </row>
-    <row r="16" spans="1:1024">
+    <row r="16" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
       <c r="M16" s="8"/>
@@ -7018,8 +6997,8 @@
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
     </row>
-    <row r="17" spans="2:18">
-      <c r="D17" s="43"/>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="D17" s="42"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="M17" s="8"/>
@@ -7028,26 +7007,26 @@
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
     </row>
-    <row r="18" spans="2:18">
-      <c r="D18" s="43"/>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="D18" s="42"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
     </row>
-    <row r="19" spans="2:18">
-      <c r="D19" s="43"/>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="D19" s="42"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
     </row>
-    <row r="20" spans="2:18">
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="J20" s="7"/>
@@ -7057,7 +7036,7 @@
       <c r="Q20" s="7"/>
       <c r="R20" s="7"/>
     </row>
-    <row r="21" spans="2:18">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="10"/>
@@ -7072,7 +7051,7 @@
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
     </row>
-    <row r="22" spans="2:18">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="10"/>
@@ -7087,7 +7066,7 @@
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
     </row>
-    <row r="23" spans="2:18">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C23" s="7"/>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
@@ -7101,7 +7080,7 @@
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
     </row>
-    <row r="24" spans="2:18">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
       <c r="J24" s="7"/>
@@ -7111,7 +7090,7 @@
       <c r="Q24" s="7"/>
       <c r="R24" s="7"/>
     </row>
-    <row r="25" spans="2:18">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
       <c r="J25" s="7"/>
@@ -7121,7 +7100,7 @@
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
     </row>
-    <row r="26" spans="2:18">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
       <c r="J26" s="7"/>
@@ -7131,7 +7110,7 @@
       <c r="Q26" s="7"/>
       <c r="R26" s="7"/>
     </row>
-    <row r="27" spans="2:18">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
       <c r="J27" s="7"/>
@@ -7141,7 +7120,7 @@
       <c r="Q27" s="7"/>
       <c r="R27" s="7"/>
     </row>
-    <row r="28" spans="2:18">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
@@ -7149,7 +7128,7 @@
       <c r="Q28" s="7"/>
       <c r="R28" s="7"/>
     </row>
-    <row r="29" spans="2:18">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G29" s="7"/>
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
@@ -7158,7 +7137,7 @@
       <c r="Q29" s="7"/>
       <c r="R29" s="7"/>
     </row>
-    <row r="30" spans="2:18">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
@@ -7166,7 +7145,7 @@
       <c r="Q30" s="7"/>
       <c r="R30" s="7"/>
     </row>
-    <row r="31" spans="2:18">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J31" s="7"/>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -7174,7 +7153,7 @@
       <c r="Q31" s="7"/>
       <c r="R31" s="7"/>
     </row>
-    <row r="32" spans="2:18">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
@@ -7182,7 +7161,7 @@
       <c r="Q32" s="7"/>
       <c r="R32" s="7"/>
     </row>
-    <row r="33" spans="2:18">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -7190,7 +7169,7 @@
       <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
     </row>
-    <row r="34" spans="2:18">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
@@ -7198,19 +7177,19 @@
       <c r="Q34" s="7"/>
       <c r="R34" s="7"/>
     </row>
-    <row r="35" spans="2:18">
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
       <c r="P35" s="7"/>
       <c r="Q35" s="7"/>
       <c r="R35" s="7"/>
     </row>
-    <row r="36" spans="2:18">
+    <row r="36" spans="2:18" x14ac:dyDescent="0.2">
       <c r="P36" s="7"/>
       <c r="Q36" s="7"/>
       <c r="R36" s="7"/>
     </row>
-    <row r="39" spans="2:18">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -7220,7 +7199,7 @@
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
     </row>
-    <row r="40" spans="2:18">
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
@@ -7230,7 +7209,7 @@
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
     </row>
-    <row r="41" spans="2:18">
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -7240,7 +7219,7 @@
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
     </row>
-    <row r="42" spans="2:18">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="G42" s="7"/>
@@ -7249,75 +7228,75 @@
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
     </row>
-    <row r="43" spans="2:18">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
       <c r="J43" s="7"/>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
     </row>
-    <row r="44" spans="2:18">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
       <c r="J44" s="7"/>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
     </row>
-    <row r="45" spans="2:18">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G45" s="7"/>
       <c r="H45" s="7"/>
       <c r="J45" s="7"/>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
     </row>
-    <row r="46" spans="2:18">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
     </row>
-    <row r="47" spans="2:18">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J47" s="7"/>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
     </row>
-    <row r="48" spans="2:18">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G48" s="7"/>
       <c r="J48" s="7"/>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
     </row>
-    <row r="49" spans="2:12">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J49" s="7"/>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
     </row>
-    <row r="50" spans="2:12">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J50" s="7"/>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
     </row>
-    <row r="51" spans="2:12">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
     </row>
-    <row r="52" spans="2:12">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J52" s="7"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
     </row>
-    <row r="53" spans="2:12">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
     </row>
-    <row r="54" spans="2:12">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
     </row>
-    <row r="58" spans="2:12">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
@@ -7327,7 +7306,7 @@
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
     </row>
-    <row r="59" spans="2:12">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
@@ -7337,7 +7316,7 @@
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
     </row>
-    <row r="60" spans="2:12">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
@@ -7347,7 +7326,7 @@
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
     </row>
-    <row r="61" spans="2:12">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
       <c r="G61" s="7"/>
@@ -7356,71 +7335,71 @@
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
     </row>
-    <row r="62" spans="2:12">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.2">
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
       <c r="J62" s="7"/>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
     </row>
-    <row r="63" spans="2:12">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.2">
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
     </row>
-    <row r="64" spans="2:12">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.2">
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
     </row>
-    <row r="65" spans="7:12">
+    <row r="65" spans="7:12" x14ac:dyDescent="0.2">
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
     </row>
-    <row r="66" spans="7:12">
+    <row r="66" spans="7:12" x14ac:dyDescent="0.2">
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
     </row>
-    <row r="67" spans="7:12">
+    <row r="67" spans="7:12" x14ac:dyDescent="0.2">
       <c r="G67" s="7"/>
       <c r="J67" s="7"/>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
     </row>
-    <row r="68" spans="7:12">
+    <row r="68" spans="7:12" x14ac:dyDescent="0.2">
       <c r="J68" s="7"/>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
     </row>
-    <row r="69" spans="7:12">
+    <row r="69" spans="7:12" x14ac:dyDescent="0.2">
       <c r="J69" s="7"/>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
     </row>
-    <row r="70" spans="7:12">
+    <row r="70" spans="7:12" x14ac:dyDescent="0.2">
       <c r="J70" s="7"/>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
     </row>
-    <row r="71" spans="7:12">
+    <row r="71" spans="7:12" x14ac:dyDescent="0.2">
       <c r="J71" s="7"/>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
     </row>
-    <row r="72" spans="7:12">
+    <row r="72" spans="7:12" x14ac:dyDescent="0.2">
       <c r="J72" s="7"/>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
     </row>
-    <row r="73" spans="7:12">
+    <row r="73" spans="7:12" x14ac:dyDescent="0.2">
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
     </row>
@@ -7440,23 +7419,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E0F765-C5B1-654D-95FF-016841AE7F76}">
   <dimension ref="A1:AMJ57"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="58" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7.625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="1024" width="11.125" style="9"/>
+    <col min="2" max="3" width="7.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="1024" width="11.1640625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="26.25">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:18" ht="27" x14ac:dyDescent="0.2">
+      <c r="A1" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="58"/>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="56"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
         <v>40</v>
       </c>
@@ -7483,7 +7462,7 @@
       <c r="Q2" s="13"/>
       <c r="R2" s="13"/>
     </row>
-    <row r="3" spans="1:18" s="9" customFormat="1">
+    <row r="3" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -7495,19 +7474,19 @@
       <c r="I3" s="10"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:18" s="9" customFormat="1" ht="26.25">
-      <c r="A4" s="56" t="s">
+    <row r="4" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A4" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="58"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="56"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="I4" s="10"/>
       <c r="O4" s="10"/>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1">
+    <row r="5" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
         <v>40</v>
       </c>
@@ -7525,17 +7504,17 @@
       <c r="I5" s="10"/>
       <c r="O5" s="10"/>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1">
+    <row r="6" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
         <v>1</v>
       </c>
-      <c r="B6" s="46">
+      <c r="B6" s="44">
         <v>0.12237963</v>
       </c>
-      <c r="C6" s="46">
+      <c r="C6" s="44">
         <v>1.7971871E-2</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="44">
         <v>-8.4463902000000007E-3</v>
       </c>
       <c r="E6" s="10"/>
@@ -7545,13 +7524,13 @@
       <c r="I6" s="10"/>
       <c r="O6" s="10"/>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="26.25">
-      <c r="A7" s="56" t="s">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A7" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="58"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="56"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
@@ -7559,7 +7538,7 @@
       <c r="I7" s="10"/>
       <c r="O7" s="10"/>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1">
+    <row r="8" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
         <v>40</v>
       </c>
@@ -7579,17 +7558,17 @@
       <c r="I8" s="10"/>
       <c r="O8" s="10"/>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1">
+    <row r="9" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>1</v>
       </c>
-      <c r="B9" s="46">
+      <c r="B9" s="44">
         <v>0.12229652000000001</v>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="44">
         <v>1.8243604E-2</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="44">
         <v>-8.6323319999999995E-3</v>
       </c>
       <c r="E9" s="12"/>
@@ -7604,13 +7583,13 @@
       <c r="N9" s="10"/>
       <c r="O9" s="10"/>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="26.25">
-      <c r="A10" s="56" t="s">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A10" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="58"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="56"/>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="I10" s="10"/>
@@ -7618,7 +7597,7 @@
       <c r="N10" s="10"/>
       <c r="O10" s="10"/>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1">
+    <row r="11" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
         <v>40</v>
       </c>
@@ -7638,17 +7617,17 @@
       <c r="N11" s="10"/>
       <c r="O11" s="10"/>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1">
+    <row r="12" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
         <v>1</v>
       </c>
-      <c r="B12" s="46">
+      <c r="B12" s="44">
         <v>0.12094782</v>
       </c>
-      <c r="C12" s="46">
+      <c r="C12" s="44">
         <v>1.9714344000000002E-2</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="44">
         <v>-9.8400616999999996E-3</v>
       </c>
       <c r="E12" s="10"/>
@@ -7658,7 +7637,7 @@
       <c r="N12" s="10"/>
       <c r="O12" s="10"/>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1">
+    <row r="13" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -7672,13 +7651,13 @@
       <c r="N13" s="10"/>
       <c r="O13" s="10"/>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="26.25">
-      <c r="A14" s="55" t="s">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A14" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
@@ -7688,13 +7667,13 @@
       <c r="N14" s="10"/>
       <c r="O14" s="10"/>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="26.25">
-      <c r="A15" s="55" t="s">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A15" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
@@ -7704,7 +7683,7 @@
       <c r="N15" s="10"/>
       <c r="O15" s="10"/>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1">
+    <row r="16" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -7718,11 +7697,11 @@
       <c r="N16" s="10"/>
       <c r="O16" s="10"/>
     </row>
-    <row r="17" spans="1:15" s="9" customFormat="1">
+    <row r="17" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10"/>
-      <c r="B17" s="46"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
@@ -7732,11 +7711,11 @@
       <c r="N17" s="10"/>
       <c r="O17" s="10"/>
     </row>
-    <row r="18" spans="1:15" s="9" customFormat="1">
+    <row r="18" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
@@ -7746,10 +7725,10 @@
       <c r="N18" s="10"/>
       <c r="O18" s="10"/>
     </row>
-    <row r="19" spans="1:15" s="9" customFormat="1">
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
+    <row r="19" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
@@ -7762,12 +7741,12 @@
       <c r="N19" s="10"/>
       <c r="O19" s="10"/>
     </row>
-    <row r="20" spans="1:15" s="9" customFormat="1">
+    <row r="20" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
       <c r="O20" s="10"/>
     </row>
-    <row r="21" spans="1:15" s="9" customFormat="1">
+    <row r="21" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -7783,7 +7762,7 @@
       <c r="M21" s="10"/>
       <c r="N21" s="10"/>
     </row>
-    <row r="22" spans="1:15" s="9" customFormat="1">
+    <row r="22" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10"/>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
@@ -7799,7 +7778,7 @@
       <c r="M22" s="10"/>
       <c r="N22" s="10"/>
     </row>
-    <row r="23" spans="1:15" s="9" customFormat="1">
+    <row r="23" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
@@ -7807,19 +7786,19 @@
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
     </row>
-    <row r="24" spans="1:15" s="9" customFormat="1">
+    <row r="24" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="I24" s="10"/>
     </row>
-    <row r="25" spans="1:15" s="9" customFormat="1">
+    <row r="25" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="10"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="I25" s="10"/>
     </row>
-    <row r="26" spans="1:15" s="9" customFormat="1">
+    <row r="26" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -7828,7 +7807,7 @@
       <c r="F26" s="10"/>
       <c r="I26" s="10"/>
     </row>
-    <row r="27" spans="1:15" s="9" customFormat="1">
+    <row r="27" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
@@ -7837,7 +7816,7 @@
       <c r="F27" s="10"/>
       <c r="I27" s="10"/>
     </row>
-    <row r="28" spans="1:15" s="9" customFormat="1">
+    <row r="28" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
@@ -7846,7 +7825,7 @@
       <c r="F28" s="10"/>
       <c r="I28" s="10"/>
     </row>
-    <row r="29" spans="1:15" s="9" customFormat="1">
+    <row r="29" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
@@ -7855,7 +7834,7 @@
       <c r="F29" s="10"/>
       <c r="I29" s="10"/>
     </row>
-    <row r="30" spans="1:15" s="9" customFormat="1">
+    <row r="30" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -7866,7 +7845,7 @@
       <c r="H30" s="10"/>
       <c r="I30" s="10"/>
     </row>
-    <row r="31" spans="1:15" s="9" customFormat="1">
+    <row r="31" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
@@ -7877,7 +7856,7 @@
       <c r="H31" s="10"/>
       <c r="I31" s="10"/>
     </row>
-    <row r="32" spans="1:15" s="9" customFormat="1">
+    <row r="32" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="10"/>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
@@ -7888,7 +7867,7 @@
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
     </row>
-    <row r="33" spans="1:12" s="9" customFormat="1">
+    <row r="33" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
@@ -7899,7 +7878,7 @@
       <c r="H33" s="10"/>
       <c r="I33" s="10"/>
     </row>
-    <row r="34" spans="1:12" s="9" customFormat="1">
+    <row r="34" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
@@ -7910,7 +7889,7 @@
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
     </row>
-    <row r="35" spans="1:12" s="9" customFormat="1">
+    <row r="35" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
@@ -7921,7 +7900,7 @@
       <c r="H35" s="10"/>
       <c r="I35" s="10"/>
     </row>
-    <row r="36" spans="1:12" s="9" customFormat="1">
+    <row r="36" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
@@ -7932,7 +7911,7 @@
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
     </row>
-    <row r="37" spans="1:12" s="9" customFormat="1">
+    <row r="37" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
@@ -7943,13 +7922,13 @@
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
     </row>
-    <row r="38" spans="1:12" s="9" customFormat="1">
+    <row r="38" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
       <c r="L38" s="10"/>
     </row>
-    <row r="40" spans="1:12" s="9" customFormat="1">
+    <row r="40" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -7963,7 +7942,7 @@
       <c r="K40" s="12"/>
       <c r="L40" s="12"/>
     </row>
-    <row r="41" spans="1:12" s="9" customFormat="1">
+    <row r="41" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
@@ -7977,25 +7956,25 @@
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
     </row>
-    <row r="42" spans="1:12" s="9" customFormat="1">
+    <row r="42" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="10"/>
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
       <c r="I42" s="10"/>
     </row>
-    <row r="43" spans="1:12" s="9" customFormat="1">
+    <row r="43" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="10"/>
       <c r="E43" s="10"/>
       <c r="F43" s="10"/>
       <c r="I43" s="10"/>
     </row>
-    <row r="44" spans="1:12" s="9" customFormat="1">
+    <row r="44" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="10"/>
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
       <c r="I44" s="10"/>
     </row>
-    <row r="45" spans="1:12" s="9" customFormat="1">
+    <row r="45" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="10"/>
@@ -8004,7 +7983,7 @@
       <c r="F45" s="10"/>
       <c r="I45" s="10"/>
     </row>
-    <row r="46" spans="1:12" s="9" customFormat="1">
+    <row r="46" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="10"/>
@@ -8013,7 +7992,7 @@
       <c r="F46" s="10"/>
       <c r="I46" s="10"/>
     </row>
-    <row r="47" spans="1:12" s="9" customFormat="1">
+    <row r="47" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="10"/>
@@ -8022,7 +8001,7 @@
       <c r="F47" s="10"/>
       <c r="I47" s="10"/>
     </row>
-    <row r="48" spans="1:12" s="9" customFormat="1">
+    <row r="48" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="10"/>
@@ -8031,7 +8010,7 @@
       <c r="F48" s="10"/>
       <c r="I48" s="10"/>
     </row>
-    <row r="49" spans="1:12" s="9" customFormat="1">
+    <row r="49" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="10"/>
@@ -8042,7 +8021,7 @@
       <c r="H49" s="10"/>
       <c r="I49" s="10"/>
     </row>
-    <row r="50" spans="1:12" s="9" customFormat="1">
+    <row r="50" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="10"/>
@@ -8053,7 +8032,7 @@
       <c r="H50" s="10"/>
       <c r="I50" s="10"/>
     </row>
-    <row r="51" spans="1:12" s="9" customFormat="1">
+    <row r="51" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="10"/>
@@ -8064,7 +8043,7 @@
       <c r="H51" s="10"/>
       <c r="I51" s="10"/>
     </row>
-    <row r="52" spans="1:12" s="9" customFormat="1">
+    <row r="52" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="10"/>
@@ -8075,7 +8054,7 @@
       <c r="H52" s="10"/>
       <c r="I52" s="10"/>
     </row>
-    <row r="53" spans="1:12" s="9" customFormat="1">
+    <row r="53" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="10"/>
@@ -8086,7 +8065,7 @@
       <c r="H53" s="10"/>
       <c r="I53" s="10"/>
     </row>
-    <row r="54" spans="1:12" s="9" customFormat="1">
+    <row r="54" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="10"/>
@@ -8097,7 +8076,7 @@
       <c r="H54" s="10"/>
       <c r="I54" s="10"/>
     </row>
-    <row r="55" spans="1:12" s="9" customFormat="1">
+    <row r="55" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="10"/>
@@ -8108,7 +8087,7 @@
       <c r="H55" s="10"/>
       <c r="I55" s="10"/>
     </row>
-    <row r="56" spans="1:12" s="9" customFormat="1">
+    <row r="56" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
@@ -8119,7 +8098,7 @@
       <c r="H56" s="10"/>
       <c r="I56" s="10"/>
     </row>
-    <row r="57" spans="1:12" s="9" customFormat="1">
+    <row r="57" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="I57" s="10"/>
       <c r="J57" s="10"/>
       <c r="K57" s="10"/>
@@ -8142,82 +8121,82 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EA0DC49-B228-6142-89A2-F876D0182B62}">
   <dimension ref="A1:M23"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="25" style="6" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="11" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="26.25">
-      <c r="A1" s="63" t="s">
+    <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A1" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="65"/>
-    </row>
-    <row r="2" spans="1:13" ht="26.25">
-      <c r="A2" s="59" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="63"/>
+    </row>
+    <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A2" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-    </row>
-    <row r="3" spans="1:13" ht="26.25">
-      <c r="A3" s="59" t="s">
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+    </row>
+    <row r="3" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A3" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="60" t="s">
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="61"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="60" t="s">
+      <c r="I3" s="59"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="61"/>
-      <c r="M3" s="62"/>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="L3" s="59"/>
+      <c r="M3" s="60"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="17"/>
       <c r="B4" s="19" t="s">
         <v>51</v>
@@ -8256,7 +8235,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="10" customFormat="1">
+    <row r="5" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
         <v>55</v>
       </c>
@@ -8273,47 +8252,47 @@
       <c r="L5" s="24"/>
       <c r="M5" s="24"/>
     </row>
-    <row r="6" spans="1:13" s="10" customFormat="1" ht="26.25">
-      <c r="A6" s="66" t="s">
+    <row r="6" spans="1:13" s="10" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A6" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="66"/>
-      <c r="L6" s="66"/>
-      <c r="M6" s="66"/>
-    </row>
-    <row r="7" spans="1:13" s="10" customFormat="1" ht="26.25">
-      <c r="A7" s="59" t="s">
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+    </row>
+    <row r="7" spans="1:13" s="10" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A7" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59" t="s">
+      <c r="B7" s="57"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="60" t="s">
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="61"/>
-      <c r="J7" s="62"/>
-      <c r="K7" s="60" t="s">
+      <c r="I7" s="59"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="61"/>
-      <c r="M7" s="62"/>
-    </row>
-    <row r="8" spans="1:13" s="10" customFormat="1">
+      <c r="L7" s="59"/>
+      <c r="M7" s="60"/>
+    </row>
+    <row r="8" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="19"/>
       <c r="B8" s="19" t="s">
         <v>51</v>
@@ -8352,7 +8331,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="10" customFormat="1">
+    <row r="9" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
         <v>55</v>
       </c>
@@ -8374,66 +8353,66 @@
       <c r="G9" s="10">
         <v>3.6160837943431828E-3</v>
       </c>
-      <c r="H9" s="48">
+      <c r="H9" s="46">
         <v>0.11176000000000004</v>
       </c>
       <c r="I9" s="10">
         <v>0.10832250629535521</v>
       </c>
-      <c r="J9" s="48">
+      <c r="J9" s="46">
         <v>3.437493704644828E-3</v>
       </c>
-      <c r="K9" s="48">
+      <c r="K9" s="46">
         <v>0.1111504</v>
       </c>
       <c r="L9" s="10">
         <v>0.10777041101452735</v>
       </c>
-      <c r="M9" s="48">
+      <c r="M9" s="46">
         <v>3.3799889854726549E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="10" customFormat="1" ht="26.25">
-      <c r="A10" s="59" t="s">
+    <row r="10" spans="1:13" s="10" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A10" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="59"/>
-      <c r="J10" s="59"/>
-      <c r="K10" s="59"/>
-      <c r="L10" s="59"/>
-      <c r="M10" s="59"/>
-    </row>
-    <row r="11" spans="1:13" s="10" customFormat="1" ht="26.25">
-      <c r="A11" s="59" t="s">
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="57"/>
+    </row>
+    <row r="11" spans="1:13" s="10" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A11" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59" t="s">
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="60" t="s">
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="61"/>
-      <c r="J11" s="62"/>
-      <c r="K11" s="60" t="s">
+      <c r="I11" s="59"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="61"/>
-      <c r="M11" s="62"/>
-    </row>
-    <row r="12" spans="1:13" s="10" customFormat="1">
+      <c r="L11" s="59"/>
+      <c r="M11" s="60"/>
+    </row>
+    <row r="12" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="19"/>
       <c r="B12" s="19" t="s">
         <v>51</v>
@@ -8472,7 +8451,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:13" s="10" customFormat="1">
+    <row r="13" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
         <v>55</v>
       </c>
@@ -8482,7 +8461,7 @@
       <c r="C13" s="10">
         <v>9.9887417128944764E-2</v>
       </c>
-      <c r="D13" s="48">
+      <c r="D13" s="46">
         <v>3.9477828710552613E-3</v>
       </c>
       <c r="E13" s="10">
@@ -8491,7 +8470,7 @@
       <c r="F13" s="10">
         <v>0.10503484422060456</v>
       </c>
-      <c r="G13" s="48">
+      <c r="G13" s="46">
         <v>3.575555779395456E-3</v>
       </c>
       <c r="H13" s="10">
@@ -8500,7 +8479,7 @@
       <c r="I13" s="10">
         <v>0.10641471667226136</v>
       </c>
-      <c r="J13" s="48">
+      <c r="J13" s="46">
         <v>3.4148833277386648E-3</v>
       </c>
       <c r="K13" s="10">
@@ -8509,51 +8488,51 @@
       <c r="L13" s="10">
         <v>0.10635354265538903</v>
       </c>
-      <c r="M13" s="48">
+      <c r="M13" s="46">
         <v>3.3744573446110068E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="10" customFormat="1" ht="26.25">
-      <c r="A14" s="59" t="s">
+    <row r="14" spans="1:13" s="10" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A14" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="59"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="59"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="59"/>
-      <c r="L14" s="59"/>
-      <c r="M14" s="59"/>
-    </row>
-    <row r="15" spans="1:13" s="10" customFormat="1" ht="26.25">
-      <c r="A15" s="59" t="s">
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="57"/>
+    </row>
+    <row r="15" spans="1:13" s="10" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A15" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59" t="s">
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="60" t="s">
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="61"/>
-      <c r="J15" s="62"/>
-      <c r="K15" s="60" t="s">
+      <c r="I15" s="59"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="61"/>
-      <c r="M15" s="62"/>
-    </row>
-    <row r="16" spans="1:13" s="10" customFormat="1">
+      <c r="L15" s="59"/>
+      <c r="M15" s="60"/>
+    </row>
+    <row r="16" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="19"/>
       <c r="B16" s="19" t="s">
         <v>51</v>
@@ -8592,7 +8571,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:13" s="10" customFormat="1">
+    <row r="17" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="19" t="s">
         <v>55</v>
       </c>
@@ -8608,7 +8587,7 @@
       <c r="E17" s="10">
         <v>0.10891520000000005</v>
       </c>
-      <c r="F17" s="48">
+      <c r="F17" s="46">
         <v>0.10546247185962908</v>
       </c>
       <c r="G17" s="10">
@@ -8617,7 +8596,7 @@
       <c r="H17" s="10">
         <v>0.10891520000000005</v>
       </c>
-      <c r="I17" s="48">
+      <c r="I17" s="46">
         <v>0.1057175724672116</v>
       </c>
       <c r="J17" s="10">
@@ -8633,26 +8612,26 @@
         <v>3.0924759115129848E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="42"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="42"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="47"/>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" s="41"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" s="41"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" s="45"/>
       <c r="E21"/>
     </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="47"/>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" s="45"/>
       <c r="E22"/>
     </row>
-    <row r="23" spans="1:13">
-      <c r="E23" s="47"/>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="E23" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -8685,82 +8664,82 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63424B91-982A-6F4D-9CA3-A2EB040E3D0E}">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="25" style="6" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="11" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="26.25">
-      <c r="A1" s="63" t="s">
+    <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A1" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="65"/>
-    </row>
-    <row r="2" spans="1:13" ht="26.25">
-      <c r="A2" s="59" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="63"/>
+    </row>
+    <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A2" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-    </row>
-    <row r="3" spans="1:13" ht="26.25">
-      <c r="A3" s="59" t="s">
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+    </row>
+    <row r="3" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A3" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="60" t="s">
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="61"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="60" t="s">
+      <c r="I3" s="59"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="61"/>
-      <c r="M3" s="62"/>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="L3" s="59"/>
+      <c r="M3" s="60"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="17"/>
       <c r="B4" s="19" t="s">
         <v>51</v>
@@ -8799,7 +8778,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
         <v>55</v>
       </c>
@@ -8816,47 +8795,47 @@
       <c r="L5" s="30"/>
       <c r="M5" s="30"/>
     </row>
-    <row r="6" spans="1:13" ht="26.25">
-      <c r="A6" s="67" t="s">
+    <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A6" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="69"/>
-    </row>
-    <row r="7" spans="1:13" ht="26.25">
-      <c r="A7" s="59" t="s">
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="67"/>
+    </row>
+    <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A7" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59" t="s">
+      <c r="B7" s="57"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="60" t="s">
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="61"/>
-      <c r="J7" s="62"/>
-      <c r="K7" s="60" t="s">
+      <c r="I7" s="59"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="61"/>
-      <c r="M7" s="62"/>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="L7" s="59"/>
+      <c r="M7" s="60"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="19" t="s">
         <v>51</v>
@@ -8895,88 +8874,88 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="44" customFormat="1">
-      <c r="A9" s="49" t="s">
+    <row r="9" spans="1:13" s="43" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="50">
+      <c r="B9" s="48">
         <v>0.10596880000000003</v>
       </c>
-      <c r="C9" s="44">
+      <c r="C9" s="43">
         <v>9.943743241827957E-2</v>
       </c>
-      <c r="D9" s="50">
+      <c r="D9" s="48">
         <v>6.531367581720458E-3</v>
       </c>
-      <c r="E9" s="50">
+      <c r="E9" s="48">
         <v>0.11125200000000002</v>
       </c>
-      <c r="F9" s="44">
+      <c r="F9" s="43">
         <v>0.10520550398784657</v>
       </c>
-      <c r="G9" s="50">
+      <c r="G9" s="48">
         <v>6.0464960121534373E-3</v>
       </c>
-      <c r="H9" s="50">
+      <c r="H9" s="48">
         <v>0.11176000000000003</v>
       </c>
-      <c r="I9" s="44">
+      <c r="I9" s="43">
         <v>0.10594924931811035</v>
       </c>
-      <c r="J9" s="50">
+      <c r="J9" s="48">
         <v>5.8107506818896766E-3</v>
       </c>
-      <c r="K9" s="50">
+      <c r="K9" s="48">
         <v>0.11115040000000004</v>
       </c>
-      <c r="L9" s="44">
+      <c r="L9" s="43">
         <v>0.10539781515256269</v>
       </c>
-      <c r="M9" s="50">
+      <c r="M9" s="48">
         <v>5.7525848474373423E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="26.25">
-      <c r="A10" s="59" t="s">
+    <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A10" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="59"/>
-      <c r="J10" s="59"/>
-      <c r="K10" s="59"/>
-      <c r="L10" s="59"/>
-      <c r="M10" s="59"/>
-    </row>
-    <row r="11" spans="1:13" ht="26.25">
-      <c r="A11" s="59" t="s">
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="57"/>
+    </row>
+    <row r="11" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A11" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59" t="s">
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="60" t="s">
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="61"/>
-      <c r="J11" s="62"/>
-      <c r="K11" s="60" t="s">
+      <c r="I11" s="59"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="61"/>
-      <c r="M11" s="62"/>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="L11" s="59"/>
+      <c r="M11" s="60"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="17"/>
       <c r="B12" s="19" t="s">
         <v>51</v>
@@ -9015,88 +8994,88 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:13" s="44" customFormat="1">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:13" s="43" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="44">
+      <c r="B13" s="43">
         <v>0.10383520000000004</v>
       </c>
-      <c r="C13" s="44">
+      <c r="C13" s="43">
         <v>9.7396777838843707E-2</v>
       </c>
-      <c r="D13" s="44">
+      <c r="D13" s="43">
         <v>6.4384221611563331E-3</v>
       </c>
-      <c r="E13" s="44">
+      <c r="E13" s="43">
         <v>0.10861040000000001</v>
       </c>
-      <c r="F13" s="44">
+      <c r="F13" s="43">
         <v>0.10266997381408707</v>
       </c>
-      <c r="G13" s="44">
+      <c r="G13" s="43">
         <v>5.9404261859129408E-3</v>
       </c>
-      <c r="H13" s="44">
+      <c r="H13" s="43">
         <v>0.1098296</v>
       </c>
-      <c r="I13" s="44">
+      <c r="I13" s="43">
         <v>0.10414909787735033</v>
       </c>
-      <c r="J13" s="44">
+      <c r="J13" s="43">
         <v>5.6805021226496782E-3</v>
       </c>
-      <c r="K13" s="44">
+      <c r="K13" s="43">
         <v>0.10972800000000005</v>
       </c>
-      <c r="L13" s="44">
+      <c r="L13" s="43">
         <v>0.10406200449145965</v>
       </c>
-      <c r="M13" s="44">
+      <c r="M13" s="43">
         <v>5.6659955085403974E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="26.25">
-      <c r="A14" s="59" t="s">
+    <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A14" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="59"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="59"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="59"/>
-      <c r="L14" s="59"/>
-      <c r="M14" s="59"/>
-    </row>
-    <row r="15" spans="1:13" ht="26.25">
-      <c r="A15" s="59" t="s">
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="57"/>
+    </row>
+    <row r="15" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A15" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59" t="s">
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="60" t="s">
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="61"/>
-      <c r="J15" s="62"/>
-      <c r="K15" s="60" t="s">
+      <c r="I15" s="59"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="61"/>
-      <c r="M15" s="62"/>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="L15" s="59"/>
+      <c r="M15" s="60"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="17"/>
       <c r="B16" s="19" t="s">
         <v>51</v>
@@ -9135,44 +9114,44 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:13" s="44" customFormat="1">
-      <c r="A17" s="49" t="s">
+    <row r="17" spans="1:13" s="43" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="44">
+      <c r="B17" s="43">
         <v>0.10322560000000003</v>
       </c>
-      <c r="C17" s="44">
+      <c r="C17" s="43">
         <v>9.7104120664805019E-2</v>
       </c>
-      <c r="D17" s="44">
+      <c r="D17" s="43">
         <v>6.1214793351950045E-3</v>
       </c>
-      <c r="E17" s="44">
+      <c r="E17" s="43">
         <v>0.10891520000000003</v>
       </c>
-      <c r="F17" s="44">
+      <c r="F17" s="43">
         <v>0.10330747020560797</v>
       </c>
-      <c r="G17" s="44">
+      <c r="G17" s="43">
         <v>5.6077297943920544E-3</v>
       </c>
-      <c r="H17" s="44">
+      <c r="H17" s="43">
         <v>0.10891520000000003</v>
       </c>
-      <c r="I17" s="44">
+      <c r="I17" s="43">
         <v>0.10339783374535956</v>
       </c>
-      <c r="J17" s="44">
+      <c r="J17" s="43">
         <v>5.5173662546404659E-3</v>
       </c>
-      <c r="K17" s="44">
+      <c r="K17" s="43">
         <v>0.10871200000000002</v>
       </c>
-      <c r="L17" s="44">
+      <c r="L17" s="43">
         <v>0.10331172489724866</v>
       </c>
-      <c r="M17" s="44">
+      <c r="M17" s="43">
         <v>5.4002751027513564E-3</v>
       </c>
     </row>
@@ -9207,81 +9186,81 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A7A1387-86E1-1C48-801D-0EFBC2B89D22}">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="26.25">
-      <c r="A1" s="63" t="s">
+    <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A1" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="70"/>
-    </row>
-    <row r="2" spans="1:13" ht="26.25">
-      <c r="A2" s="60" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="68"/>
+    </row>
+    <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A2" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="62"/>
-    </row>
-    <row r="3" spans="1:13" s="6" customFormat="1" ht="26.25">
-      <c r="A3" s="59" t="s">
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="60"/>
+    </row>
+    <row r="3" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A3" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="60" t="s">
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="61"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="60" t="s">
+      <c r="I3" s="59"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="61"/>
-      <c r="M3" s="62"/>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="L3" s="59"/>
+      <c r="M3" s="60"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="33"/>
       <c r="B4" s="32" t="s">
         <v>51</v>
@@ -9320,7 +9299,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="31" t="s">
         <v>55</v>
       </c>
@@ -9337,47 +9316,47 @@
       <c r="L5" s="34"/>
       <c r="M5" s="34"/>
     </row>
-    <row r="6" spans="1:13" ht="26.25">
-      <c r="A6" s="60" t="s">
+    <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A6" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="62"/>
-    </row>
-    <row r="7" spans="1:13" s="6" customFormat="1" ht="26.25">
-      <c r="A7" s="59" t="s">
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="60"/>
+    </row>
+    <row r="7" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A7" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59" t="s">
+      <c r="B7" s="57"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="60" t="s">
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="61"/>
-      <c r="J7" s="62"/>
-      <c r="K7" s="60" t="s">
+      <c r="I7" s="59"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="61"/>
-      <c r="M7" s="62"/>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="L7" s="59"/>
+      <c r="M7" s="60"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="33"/>
       <c r="B8" s="32" t="s">
         <v>51</v>
@@ -9416,7 +9395,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="31" t="s">
         <v>55</v>
       </c>
@@ -9433,47 +9412,47 @@
       <c r="L9" s="24"/>
       <c r="M9" s="24"/>
     </row>
-    <row r="10" spans="1:13" ht="26.25">
-      <c r="A10" s="60" t="s">
+    <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A10" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="61"/>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="61"/>
-      <c r="M10" s="62"/>
-    </row>
-    <row r="11" spans="1:13" s="6" customFormat="1" ht="26.25">
-      <c r="A11" s="59" t="s">
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="59"/>
+      <c r="L10" s="59"/>
+      <c r="M10" s="60"/>
+    </row>
+    <row r="11" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A11" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59" t="s">
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="60" t="s">
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="61"/>
-      <c r="J11" s="62"/>
-      <c r="K11" s="60" t="s">
+      <c r="I11" s="59"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="61"/>
-      <c r="M11" s="62"/>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="L11" s="59"/>
+      <c r="M11" s="60"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="33"/>
       <c r="B12" s="32" t="s">
         <v>51</v>
@@ -9512,7 +9491,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="31" t="s">
         <v>55</v>
       </c>
@@ -9529,47 +9508,47 @@
       <c r="L13" s="36"/>
       <c r="M13" s="36"/>
     </row>
-    <row r="14" spans="1:13" ht="26.25">
-      <c r="A14" s="60" t="s">
+    <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A14" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
-      <c r="L14" s="61"/>
-      <c r="M14" s="62"/>
-    </row>
-    <row r="15" spans="1:13" s="6" customFormat="1" ht="26.25">
-      <c r="A15" s="59" t="s">
+      <c r="B14" s="59"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="59"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="59"/>
+      <c r="L14" s="59"/>
+      <c r="M14" s="60"/>
+    </row>
+    <row r="15" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A15" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59" t="s">
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="60" t="s">
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="61"/>
-      <c r="J15" s="62"/>
-      <c r="K15" s="60" t="s">
+      <c r="I15" s="59"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="61"/>
-      <c r="M15" s="62"/>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="L15" s="59"/>
+      <c r="M15" s="60"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="33"/>
       <c r="B16" s="32" t="s">
         <v>51</v>
@@ -9608,7 +9587,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="31" t="s">
         <v>55</v>
       </c>
@@ -9656,23 +9635,23 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AMJ69"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="58" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7.625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="1024" width="11.125" style="9"/>
+    <col min="2" max="3" width="7.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="1024" width="11.1640625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="26.25">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:18" ht="27" x14ac:dyDescent="0.2">
+      <c r="A1" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="58"/>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="56"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
         <v>40</v>
       </c>
@@ -9699,7 +9678,7 @@
       <c r="Q2" s="13"/>
       <c r="R2" s="13"/>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>0</v>
       </c>
@@ -9720,7 +9699,7 @@
       <c r="Q3" s="10"/>
       <c r="R3" s="10"/>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
         <v>0.5</v>
       </c>
@@ -9732,7 +9711,7 @@
       <c r="I4" s="10"/>
       <c r="O4" s="10"/>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <v>1.5</v>
       </c>
@@ -9744,7 +9723,7 @@
       <c r="I5" s="10"/>
       <c r="O5" s="10"/>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
         <v>-1</v>
       </c>
@@ -9756,19 +9735,19 @@
       <c r="I6" s="10"/>
       <c r="O6" s="10"/>
     </row>
-    <row r="7" spans="1:18" ht="26.25">
-      <c r="A7" s="56" t="s">
+    <row r="7" spans="1:18" ht="27" x14ac:dyDescent="0.2">
+      <c r="A7" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="58"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="56"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="I7" s="10"/>
       <c r="O7" s="10"/>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
         <v>40</v>
       </c>
@@ -9786,7 +9765,7 @@
       <c r="I8" s="10"/>
       <c r="O8" s="10"/>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>0</v>
       </c>
@@ -9800,7 +9779,7 @@
       <c r="I9" s="10"/>
       <c r="O9" s="10"/>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="11">
         <v>0.5</v>
       </c>
@@ -9814,7 +9793,7 @@
       <c r="I10" s="10"/>
       <c r="O10" s="10"/>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
         <v>1.5</v>
       </c>
@@ -9828,7 +9807,7 @@
       <c r="I11" s="10"/>
       <c r="O11" s="10"/>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
         <v>-1</v>
       </c>
@@ -9842,13 +9821,13 @@
       <c r="I12" s="10"/>
       <c r="O12" s="10"/>
     </row>
-    <row r="13" spans="1:18" ht="26.25">
-      <c r="A13" s="56" t="s">
+    <row r="13" spans="1:18" ht="27" x14ac:dyDescent="0.2">
+      <c r="A13" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="58"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="56"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
@@ -9856,7 +9835,7 @@
       <c r="I13" s="10"/>
       <c r="O13" s="10"/>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
         <v>40</v>
       </c>
@@ -9876,7 +9855,7 @@
       <c r="I14" s="10"/>
       <c r="O14" s="10"/>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="11">
         <v>0</v>
       </c>
@@ -9895,7 +9874,7 @@
       <c r="N15" s="15"/>
       <c r="O15" s="10"/>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="11">
         <v>0.5</v>
       </c>
@@ -9906,7 +9885,7 @@
       <c r="N16" s="15"/>
       <c r="O16" s="10"/>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="11">
         <v>1.5</v>
       </c>
@@ -9925,7 +9904,7 @@
       <c r="N17" s="10"/>
       <c r="O17" s="10"/>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="11">
         <v>-1</v>
       </c>
@@ -9939,13 +9918,13 @@
       <c r="N18" s="10"/>
       <c r="O18" s="10"/>
     </row>
-    <row r="19" spans="1:15" ht="26.25">
-      <c r="A19" s="56" t="s">
+    <row r="19" spans="1:15" ht="27" x14ac:dyDescent="0.2">
+      <c r="A19" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="58"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="56"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="I19" s="10"/>
@@ -9953,7 +9932,7 @@
       <c r="N19" s="10"/>
       <c r="O19" s="10"/>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="19" t="s">
         <v>40</v>
       </c>
@@ -9973,7 +9952,7 @@
       <c r="N20" s="10"/>
       <c r="O20" s="10"/>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="11">
         <v>0</v>
       </c>
@@ -9987,7 +9966,7 @@
       <c r="N21" s="10"/>
       <c r="O21" s="10"/>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="11">
         <v>0.5</v>
       </c>
@@ -10001,7 +9980,7 @@
       <c r="N22" s="10"/>
       <c r="O22" s="10"/>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="11">
         <v>1.5</v>
       </c>
@@ -10017,7 +9996,7 @@
       <c r="N23" s="10"/>
       <c r="O23" s="10"/>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="11">
         <v>-1</v>
       </c>
@@ -10033,7 +10012,7 @@
       <c r="N24" s="10"/>
       <c r="O24" s="10"/>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
@@ -10047,13 +10026,13 @@
       <c r="N25" s="10"/>
       <c r="O25" s="10"/>
     </row>
-    <row r="26" spans="1:15" ht="26.25">
-      <c r="A26" s="55" t="s">
+    <row r="26" spans="1:15" ht="27" x14ac:dyDescent="0.2">
+      <c r="A26" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="55"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -10063,13 +10042,13 @@
       <c r="N26" s="10"/>
       <c r="O26" s="10"/>
     </row>
-    <row r="27" spans="1:15" ht="26.25">
-      <c r="A27" s="55" t="s">
+    <row r="27" spans="1:15" ht="27" x14ac:dyDescent="0.2">
+      <c r="A27" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="55"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="55"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -10079,7 +10058,7 @@
       <c r="N27" s="10"/>
       <c r="O27" s="10"/>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
@@ -10093,7 +10072,7 @@
       <c r="N28" s="10"/>
       <c r="O28" s="10"/>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
@@ -10107,7 +10086,7 @@
       <c r="N29" s="10"/>
       <c r="O29" s="10"/>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -10121,7 +10100,7 @@
       <c r="N30" s="10"/>
       <c r="O30" s="10"/>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
       <c r="D31" s="10"/>
@@ -10137,12 +10116,12 @@
       <c r="N31" s="10"/>
       <c r="O31" s="10"/>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
       <c r="O32" s="10"/>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="12"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
@@ -10158,7 +10137,7 @@
       <c r="M33" s="10"/>
       <c r="N33" s="10"/>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
@@ -10174,7 +10153,7 @@
       <c r="M34" s="10"/>
       <c r="N34" s="10"/>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" s="10"/>
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
@@ -10182,19 +10161,19 @@
       <c r="M35" s="10"/>
       <c r="N35" s="10"/>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="10"/>
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
       <c r="I36" s="10"/>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="10"/>
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
       <c r="I37" s="10"/>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
@@ -10203,7 +10182,7 @@
       <c r="F38" s="10"/>
       <c r="I38" s="10"/>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="10"/>
@@ -10212,7 +10191,7 @@
       <c r="F39" s="10"/>
       <c r="I39" s="10"/>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
@@ -10221,7 +10200,7 @@
       <c r="F40" s="10"/>
       <c r="I40" s="10"/>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
@@ -10230,7 +10209,7 @@
       <c r="F41" s="10"/>
       <c r="I41" s="10"/>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
@@ -10241,7 +10220,7 @@
       <c r="H42" s="10"/>
       <c r="I42" s="10"/>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="10"/>
@@ -10252,7 +10231,7 @@
       <c r="H43" s="10"/>
       <c r="I43" s="10"/>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="10"/>
@@ -10263,7 +10242,7 @@
       <c r="H44" s="10"/>
       <c r="I44" s="10"/>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="10"/>
@@ -10274,7 +10253,7 @@
       <c r="H45" s="10"/>
       <c r="I45" s="10"/>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="10"/>
@@ -10285,7 +10264,7 @@
       <c r="H46" s="10"/>
       <c r="I46" s="10"/>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="10"/>
@@ -10296,7 +10275,7 @@
       <c r="H47" s="10"/>
       <c r="I47" s="10"/>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="10"/>
@@ -10307,7 +10286,7 @@
       <c r="H48" s="10"/>
       <c r="I48" s="10"/>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="10"/>
@@ -10318,13 +10297,13 @@
       <c r="H49" s="10"/>
       <c r="I49" s="10"/>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="I50" s="10"/>
       <c r="J50" s="10"/>
       <c r="K50" s="10"/>
       <c r="L50" s="10"/>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="12"/>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
@@ -10338,7 +10317,7 @@
       <c r="K52" s="12"/>
       <c r="L52" s="12"/>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="10"/>
@@ -10352,25 +10331,25 @@
       <c r="K53" s="10"/>
       <c r="L53" s="10"/>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="10"/>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
       <c r="I54" s="10"/>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="10"/>
       <c r="E55" s="10"/>
       <c r="F55" s="10"/>
       <c r="I55" s="10"/>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="10"/>
       <c r="E56" s="10"/>
       <c r="F56" s="10"/>
       <c r="I56" s="10"/>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="10"/>
@@ -10379,7 +10358,7 @@
       <c r="F57" s="10"/>
       <c r="I57" s="10"/>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="10"/>
       <c r="B58" s="10"/>
       <c r="C58" s="10"/>
@@ -10388,7 +10367,7 @@
       <c r="F58" s="10"/>
       <c r="I58" s="10"/>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="10"/>
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
@@ -10397,7 +10376,7 @@
       <c r="F59" s="10"/>
       <c r="I59" s="10"/>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="10"/>
       <c r="B60" s="10"/>
       <c r="C60" s="10"/>
@@ -10406,7 +10385,7 @@
       <c r="F60" s="10"/>
       <c r="I60" s="10"/>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="10"/>
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
@@ -10417,7 +10396,7 @@
       <c r="H61" s="10"/>
       <c r="I61" s="10"/>
     </row>
-    <row r="62" spans="1:12">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="10"/>
       <c r="B62" s="10"/>
       <c r="C62" s="10"/>
@@ -10428,7 +10407,7 @@
       <c r="H62" s="10"/>
       <c r="I62" s="10"/>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="10"/>
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
@@ -10439,7 +10418,7 @@
       <c r="H63" s="10"/>
       <c r="I63" s="10"/>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="10"/>
       <c r="B64" s="10"/>
       <c r="C64" s="10"/>
@@ -10450,7 +10429,7 @@
       <c r="H64" s="10"/>
       <c r="I64" s="10"/>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="10"/>
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
@@ -10461,7 +10440,7 @@
       <c r="H65" s="10"/>
       <c r="I65" s="10"/>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="10"/>
       <c r="B66" s="10"/>
       <c r="C66" s="10"/>
@@ -10472,7 +10451,7 @@
       <c r="H66" s="10"/>
       <c r="I66" s="10"/>
     </row>
-    <row r="67" spans="1:12">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="10"/>
       <c r="B67" s="10"/>
       <c r="C67" s="10"/>
@@ -10483,7 +10462,7 @@
       <c r="H67" s="10"/>
       <c r="I67" s="10"/>
     </row>
-    <row r="68" spans="1:12">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="10"/>
       <c r="B68" s="10"/>
       <c r="C68" s="10"/>
@@ -10494,7 +10473,7 @@
       <c r="H68" s="10"/>
       <c r="I68" s="10"/>
     </row>
-    <row r="69" spans="1:12">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="I69" s="10"/>
       <c r="J69" s="10"/>
       <c r="K69" s="10"/>
@@ -10517,99 +10496,99 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Q78"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.75" style="10" customWidth="1"/>
-    <col min="7" max="7" width="30.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="13.625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="30.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="13.6640625" style="6" customWidth="1"/>
     <col min="18" max="16384" width="11" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="26.25">
-      <c r="A1" s="75" t="s">
+    <row r="1" spans="1:17" ht="27" x14ac:dyDescent="0.2">
+      <c r="A1" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-    </row>
-    <row r="2" spans="1:17" ht="59.1" customHeight="1">
-      <c r="A2" s="71" t="s">
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+    </row>
+    <row r="2" spans="1:17" ht="59" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="73"/>
-    </row>
-    <row r="3" spans="1:17" s="26" customFormat="1" ht="26.25">
-      <c r="A3" s="59" t="s">
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="71"/>
+    </row>
+    <row r="3" spans="1:17" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A3" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="59"/>
-      <c r="L3" s="59"/>
-    </row>
-    <row r="4" spans="1:17" s="26" customFormat="1" ht="26.25">
-      <c r="A4" s="59" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+    </row>
+    <row r="4" spans="1:17" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A4" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="59"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59" t="s">
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="59" t="s">
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="59"/>
-      <c r="L4" s="59"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
       <c r="N4" s="18"/>
       <c r="O4" s="18"/>
       <c r="P4" s="18"/>
       <c r="Q4" s="18"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
         <v>50</v>
       </c>
@@ -10647,7 +10626,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="19">
         <v>1</v>
       </c>
@@ -10681,7 +10660,7 @@
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D7" s="19">
         <v>2</v>
       </c>
@@ -10708,7 +10687,7 @@
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D8" s="19">
         <v>3</v>
       </c>
@@ -10735,7 +10714,7 @@
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D9" s="19"/>
       <c r="E9" s="11"/>
       <c r="F9" s="19"/>
@@ -10758,7 +10737,7 @@
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
       <c r="G10" s="19">
@@ -10780,7 +10759,7 @@
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="G11" s="19">
@@ -10802,7 +10781,7 @@
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
       <c r="G12" s="19">
@@ -10824,7 +10803,7 @@
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
       <c r="G13" s="19"/>
@@ -10842,7 +10821,7 @@
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
       <c r="G14" s="10"/>
@@ -10860,7 +10839,7 @@
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
       <c r="G15" s="10"/>
@@ -10878,7 +10857,7 @@
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
       <c r="G16" s="10"/>
@@ -10896,7 +10875,7 @@
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
       <c r="G17" s="10"/>
@@ -10914,7 +10893,7 @@
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
       <c r="G18" s="10"/>
@@ -10932,7 +10911,7 @@
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
       <c r="G19" s="10"/>
@@ -10950,7 +10929,7 @@
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
       <c r="G20" s="10"/>
@@ -10968,7 +10947,7 @@
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
       <c r="G21" s="10"/>
@@ -10982,52 +10961,52 @@
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
     </row>
-    <row r="22" spans="1:17" s="26" customFormat="1" ht="26.25">
-      <c r="A22" s="74" t="s">
+    <row r="22" spans="1:17" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A22" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="74"/>
-      <c r="C22" s="74"/>
-      <c r="D22" s="74"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="74"/>
-      <c r="J22" s="74"/>
-      <c r="K22" s="74"/>
-      <c r="L22" s="74"/>
+      <c r="B22" s="72"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="72"/>
       <c r="M22" s="27"/>
       <c r="O22" s="28"/>
       <c r="P22" s="28"/>
       <c r="Q22" s="28"/>
     </row>
-    <row r="23" spans="1:17" s="26" customFormat="1" ht="26.25">
-      <c r="A23" s="59" t="s">
+    <row r="23" spans="1:17" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A23" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="59"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59" t="s">
+      <c r="B23" s="57"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59" t="s">
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="59" t="s">
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K23" s="59"/>
-      <c r="L23" s="59"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
       <c r="O23" s="28"/>
       <c r="P23" s="28"/>
       <c r="Q23" s="28"/>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="19" t="s">
         <v>50</v>
       </c>
@@ -11068,7 +11047,7 @@
       <c r="P24" s="7"/>
       <c r="Q24" s="7"/>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="19">
         <v>1</v>
       </c>
@@ -11109,7 +11088,7 @@
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D26" s="19">
         <v>2</v>
       </c>
@@ -11141,7 +11120,7 @@
       <c r="P26" s="7"/>
       <c r="Q26" s="7"/>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D27" s="19">
         <v>3</v>
       </c>
@@ -11173,7 +11152,7 @@
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D28" s="19"/>
       <c r="E28" s="10"/>
       <c r="F28" s="19"/>
@@ -11199,7 +11178,7 @@
       <c r="P28" s="7"/>
       <c r="Q28" s="7"/>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>
       <c r="G29" s="19">
@@ -11224,7 +11203,7 @@
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D30" s="10"/>
       <c r="E30" s="10"/>
       <c r="G30" s="19">
@@ -11249,7 +11228,7 @@
       <c r="P30" s="7"/>
       <c r="Q30" s="7"/>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
       <c r="G31" s="19">
@@ -11274,7 +11253,7 @@
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
     </row>
-    <row r="32" spans="1:17">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
       <c r="G32" s="19"/>
@@ -11293,7 +11272,7 @@
       <c r="P32" s="7"/>
       <c r="Q32" s="7"/>
     </row>
-    <row r="33" spans="1:17">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
       <c r="G33" s="10"/>
@@ -11312,7 +11291,7 @@
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
     </row>
-    <row r="34" spans="1:17">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
       <c r="G34" s="10"/>
@@ -11331,7 +11310,7 @@
       <c r="P34" s="7"/>
       <c r="Q34" s="7"/>
     </row>
-    <row r="35" spans="1:17">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
       <c r="G35" s="10"/>
@@ -11350,7 +11329,7 @@
       <c r="P35" s="7"/>
       <c r="Q35" s="7"/>
     </row>
-    <row r="36" spans="1:17">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
       <c r="G36" s="10"/>
@@ -11369,7 +11348,7 @@
       <c r="P36" s="7"/>
       <c r="Q36" s="7"/>
     </row>
-    <row r="37" spans="1:17">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
       <c r="G37" s="10"/>
@@ -11388,7 +11367,7 @@
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
     </row>
-    <row r="38" spans="1:17">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
       <c r="G38" s="10"/>
@@ -11407,7 +11386,7 @@
       <c r="P38" s="7"/>
       <c r="Q38" s="7"/>
     </row>
-    <row r="39" spans="1:17">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
       <c r="G39" s="10"/>
@@ -11426,7 +11405,7 @@
       <c r="P39" s="7"/>
       <c r="Q39" s="7"/>
     </row>
-    <row r="40" spans="1:17">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D40" s="10"/>
       <c r="E40" s="10"/>
       <c r="G40" s="10"/>
@@ -11439,48 +11418,48 @@
       <c r="P40" s="7"/>
       <c r="Q40" s="7"/>
     </row>
-    <row r="41" spans="1:17" s="26" customFormat="1" ht="26.25">
-      <c r="A41" s="74" t="s">
+    <row r="41" spans="1:17" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A41" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="74"/>
-      <c r="C41" s="74"/>
-      <c r="D41" s="74"/>
-      <c r="E41" s="74"/>
-      <c r="F41" s="74"/>
-      <c r="G41" s="74"/>
-      <c r="H41" s="74"/>
-      <c r="I41" s="74"/>
-      <c r="J41" s="74"/>
-      <c r="K41" s="74"/>
-      <c r="L41" s="74"/>
+      <c r="B41" s="72"/>
+      <c r="C41" s="72"/>
+      <c r="D41" s="72"/>
+      <c r="E41" s="72"/>
+      <c r="F41" s="72"/>
+      <c r="G41" s="72"/>
+      <c r="H41" s="72"/>
+      <c r="I41" s="72"/>
+      <c r="J41" s="72"/>
+      <c r="K41" s="72"/>
+      <c r="L41" s="72"/>
       <c r="O41" s="28"/>
       <c r="P41" s="28"/>
       <c r="Q41" s="28"/>
     </row>
-    <row r="42" spans="1:17" s="26" customFormat="1" ht="26.25">
-      <c r="A42" s="59" t="s">
+    <row r="42" spans="1:17" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A42" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="59"/>
-      <c r="C42" s="59"/>
-      <c r="D42" s="59" t="s">
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="59"/>
-      <c r="F42" s="59"/>
-      <c r="G42" s="59" t="s">
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H42" s="59"/>
-      <c r="I42" s="59"/>
-      <c r="J42" s="59" t="s">
+      <c r="H42" s="57"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K42" s="59"/>
-      <c r="L42" s="59"/>
-    </row>
-    <row r="43" spans="1:17">
+      <c r="K42" s="57"/>
+      <c r="L42" s="57"/>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
         <v>50</v>
       </c>
@@ -11518,7 +11497,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:17">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="19">
         <v>1</v>
       </c>
@@ -11556,7 +11535,7 @@
         <v>5.6689999999999996</v>
       </c>
     </row>
-    <row r="45" spans="1:17">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D45" s="19">
         <v>2</v>
       </c>
@@ -11585,7 +11564,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:17">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D46" s="19">
         <v>3</v>
       </c>
@@ -11614,7 +11593,7 @@
         <v>12.718999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:17">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D47" s="19"/>
       <c r="E47" s="11"/>
       <c r="F47" s="19"/>
@@ -11637,7 +11616,7 @@
         <v>16.966000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:17">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D48" s="10"/>
       <c r="G48" s="19">
         <v>5</v>
@@ -11658,7 +11637,7 @@
         <v>20.881</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D49" s="10"/>
       <c r="G49" s="19">
         <v>6</v>
@@ -11679,7 +11658,7 @@
         <v>24.969000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D50" s="10"/>
       <c r="G50" s="19">
         <v>7</v>
@@ -11700,7 +11679,7 @@
         <v>28.847999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D51" s="10"/>
       <c r="G51" s="19"/>
       <c r="H51" s="11"/>
@@ -11715,7 +11694,7 @@
         <v>33.03</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D52" s="10"/>
       <c r="G52" s="10"/>
       <c r="H52" s="10"/>
@@ -11730,7 +11709,7 @@
         <v>36.945</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D53" s="10"/>
       <c r="G53" s="10"/>
       <c r="H53" s="10"/>
@@ -11745,7 +11724,7 @@
         <v>40.929000000000002</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D54" s="10"/>
       <c r="G54" s="10"/>
       <c r="H54" s="10"/>
@@ -11760,7 +11739,7 @@
         <v>44.854999999999997</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D55" s="10"/>
       <c r="G55" s="10"/>
       <c r="H55" s="10"/>
@@ -11775,7 +11754,7 @@
         <v>50.978000000000002</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D56" s="10"/>
       <c r="E56" s="10"/>
       <c r="G56" s="10"/>
@@ -11791,7 +11770,7 @@
         <v>66.174999999999997</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D57" s="10"/>
       <c r="E57" s="10"/>
       <c r="G57" s="10"/>
@@ -11807,7 +11786,7 @@
         <v>96.876000000000005</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D58" s="10"/>
       <c r="E58" s="10"/>
       <c r="G58" s="10"/>
@@ -11823,7 +11802,7 @@
         <v>149.39099999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D59" s="10"/>
       <c r="E59" s="10"/>
       <c r="G59" s="10"/>
@@ -11833,45 +11812,45 @@
       <c r="K59" s="24"/>
       <c r="L59" s="25"/>
     </row>
-    <row r="60" spans="1:12" s="26" customFormat="1" ht="26.25">
-      <c r="A60" s="59" t="s">
+    <row r="60" spans="1:12" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A60" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="59"/>
-      <c r="C60" s="59"/>
-      <c r="D60" s="59"/>
-      <c r="E60" s="59"/>
-      <c r="F60" s="59"/>
-      <c r="G60" s="59"/>
-      <c r="H60" s="59"/>
-      <c r="I60" s="59"/>
-      <c r="J60" s="59"/>
-      <c r="K60" s="59"/>
-      <c r="L60" s="59"/>
-    </row>
-    <row r="61" spans="1:12" s="26" customFormat="1" ht="26.25">
-      <c r="A61" s="59" t="s">
+      <c r="B60" s="57"/>
+      <c r="C60" s="57"/>
+      <c r="D60" s="57"/>
+      <c r="E60" s="57"/>
+      <c r="F60" s="57"/>
+      <c r="G60" s="57"/>
+      <c r="H60" s="57"/>
+      <c r="I60" s="57"/>
+      <c r="J60" s="57"/>
+      <c r="K60" s="57"/>
+      <c r="L60" s="57"/>
+    </row>
+    <row r="61" spans="1:12" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A61" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="59"/>
-      <c r="C61" s="59"/>
-      <c r="D61" s="59" t="s">
+      <c r="B61" s="57"/>
+      <c r="C61" s="57"/>
+      <c r="D61" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="59"/>
-      <c r="F61" s="59"/>
-      <c r="G61" s="59" t="s">
+      <c r="E61" s="57"/>
+      <c r="F61" s="57"/>
+      <c r="G61" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H61" s="59"/>
-      <c r="I61" s="59"/>
-      <c r="J61" s="59" t="s">
+      <c r="H61" s="57"/>
+      <c r="I61" s="57"/>
+      <c r="J61" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="59"/>
-      <c r="L61" s="59"/>
-    </row>
-    <row r="62" spans="1:12">
+      <c r="K61" s="57"/>
+      <c r="L61" s="57"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
         <v>50</v>
       </c>
@@ -11909,7 +11888,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="19">
         <v>1</v>
       </c>
@@ -11947,7 +11926,7 @@
         <v>5.6689999999999996</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D64" s="19">
         <v>2</v>
       </c>
@@ -11976,7 +11955,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="4:12">
+    <row r="65" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D65" s="19">
         <v>3</v>
       </c>
@@ -12005,7 +11984,7 @@
         <v>12.718999999999999</v>
       </c>
     </row>
-    <row r="66" spans="4:12">
+    <row r="66" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D66" s="19"/>
       <c r="E66" s="11"/>
       <c r="F66" s="19"/>
@@ -12028,7 +12007,7 @@
         <v>16.966000000000001</v>
       </c>
     </row>
-    <row r="67" spans="4:12">
+    <row r="67" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D67" s="10"/>
       <c r="E67" s="10"/>
       <c r="G67" s="19">
@@ -12050,7 +12029,7 @@
         <v>20.881</v>
       </c>
     </row>
-    <row r="68" spans="4:12">
+    <row r="68" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D68" s="10"/>
       <c r="E68" s="10"/>
       <c r="G68" s="19">
@@ -12072,7 +12051,7 @@
         <v>24.969000000000001</v>
       </c>
     </row>
-    <row r="69" spans="4:12">
+    <row r="69" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D69" s="10"/>
       <c r="E69" s="10"/>
       <c r="G69" s="19">
@@ -12094,7 +12073,7 @@
         <v>28.847999999999999</v>
       </c>
     </row>
-    <row r="70" spans="4:12">
+    <row r="70" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D70" s="10"/>
       <c r="E70" s="10"/>
       <c r="G70" s="19"/>
@@ -12110,7 +12089,7 @@
         <v>33.03</v>
       </c>
     </row>
-    <row r="71" spans="4:12">
+    <row r="71" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D71" s="10"/>
       <c r="E71" s="10"/>
       <c r="G71" s="10"/>
@@ -12126,7 +12105,7 @@
         <v>36.945</v>
       </c>
     </row>
-    <row r="72" spans="4:12">
+    <row r="72" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D72" s="10"/>
       <c r="E72" s="10"/>
       <c r="G72" s="10"/>
@@ -12142,7 +12121,7 @@
         <v>40.929000000000002</v>
       </c>
     </row>
-    <row r="73" spans="4:12">
+    <row r="73" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D73" s="10"/>
       <c r="E73" s="10"/>
       <c r="G73" s="10"/>
@@ -12158,7 +12137,7 @@
         <v>44.854999999999997</v>
       </c>
     </row>
-    <row r="74" spans="4:12">
+    <row r="74" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D74" s="10"/>
       <c r="E74" s="10"/>
       <c r="G74" s="10"/>
@@ -12174,7 +12153,7 @@
         <v>50.978000000000002</v>
       </c>
     </row>
-    <row r="75" spans="4:12">
+    <row r="75" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D75" s="10"/>
       <c r="E75" s="10"/>
       <c r="G75" s="10"/>
@@ -12190,7 +12169,7 @@
         <v>66.174999999999997</v>
       </c>
     </row>
-    <row r="76" spans="4:12">
+    <row r="76" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D76" s="10"/>
       <c r="E76" s="10"/>
       <c r="G76" s="10"/>
@@ -12206,7 +12185,7 @@
         <v>96.876000000000005</v>
       </c>
     </row>
-    <row r="77" spans="4:12">
+    <row r="77" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D77" s="10"/>
       <c r="E77" s="10"/>
       <c r="G77" s="10"/>
@@ -12222,7 +12201,7 @@
         <v>149.39099999999999</v>
       </c>
     </row>
-    <row r="78" spans="4:12">
+    <row r="78" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D78" s="10"/>
       <c r="E78" s="10"/>
       <c r="G78" s="10"/>
@@ -12265,99 +12244,99 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{675AB273-2180-584F-8A66-E764000A71E7}">
   <dimension ref="A1:Q78"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.75" style="10" customWidth="1"/>
-    <col min="7" max="7" width="30.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="13.625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="30.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="13.6640625" style="6" customWidth="1"/>
     <col min="18" max="16384" width="11" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="26.25">
-      <c r="A1" s="75" t="s">
+    <row r="1" spans="1:17" ht="27" x14ac:dyDescent="0.2">
+      <c r="A1" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-    </row>
-    <row r="2" spans="1:17" ht="59.1" customHeight="1">
-      <c r="A2" s="71" t="s">
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+    </row>
+    <row r="2" spans="1:17" ht="59" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="73"/>
-    </row>
-    <row r="3" spans="1:17" s="26" customFormat="1" ht="26.25">
-      <c r="A3" s="59" t="s">
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="71"/>
+    </row>
+    <row r="3" spans="1:17" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A3" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="59"/>
-      <c r="L3" s="59"/>
-    </row>
-    <row r="4" spans="1:17" s="26" customFormat="1" ht="26.25">
-      <c r="A4" s="59" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+    </row>
+    <row r="4" spans="1:17" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A4" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="59"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59" t="s">
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="59" t="s">
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="59"/>
-      <c r="L4" s="59"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="40"/>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
         <v>50</v>
       </c>
@@ -12395,7 +12374,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="19">
         <v>1</v>
       </c>
@@ -12429,7 +12408,7 @@
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D7" s="19">
         <v>2</v>
       </c>
@@ -12456,7 +12435,7 @@
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D8" s="19">
         <v>3</v>
       </c>
@@ -12483,7 +12462,7 @@
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D9" s="19"/>
       <c r="E9" s="11"/>
       <c r="F9" s="19"/>
@@ -12506,7 +12485,7 @@
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
       <c r="G10" s="19">
@@ -12528,7 +12507,7 @@
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="G11" s="19">
@@ -12550,7 +12529,7 @@
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
       <c r="G12" s="19">
@@ -12572,7 +12551,7 @@
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
       <c r="G13" s="19"/>
@@ -12590,7 +12569,7 @@
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
       <c r="G14" s="10"/>
@@ -12608,7 +12587,7 @@
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
       <c r="G15" s="10"/>
@@ -12626,7 +12605,7 @@
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
       <c r="G16" s="10"/>
@@ -12644,7 +12623,7 @@
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
       <c r="G17" s="10"/>
@@ -12662,7 +12641,7 @@
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
       <c r="G18" s="10"/>
@@ -12680,7 +12659,7 @@
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
       <c r="G19" s="10"/>
@@ -12698,7 +12677,7 @@
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
       <c r="G20" s="10"/>
@@ -12716,7 +12695,7 @@
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
       <c r="G21" s="10"/>
@@ -12730,52 +12709,52 @@
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
     </row>
-    <row r="22" spans="1:17" s="26" customFormat="1" ht="26.25">
-      <c r="A22" s="74" t="s">
+    <row r="22" spans="1:17" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A22" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="74"/>
-      <c r="C22" s="74"/>
-      <c r="D22" s="74"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="74"/>
-      <c r="J22" s="74"/>
-      <c r="K22" s="74"/>
-      <c r="L22" s="74"/>
+      <c r="B22" s="72"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="72"/>
       <c r="M22" s="27"/>
       <c r="O22" s="28"/>
       <c r="P22" s="28"/>
       <c r="Q22" s="28"/>
     </row>
-    <row r="23" spans="1:17" s="26" customFormat="1" ht="26.25">
-      <c r="A23" s="59" t="s">
+    <row r="23" spans="1:17" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A23" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="59"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59" t="s">
+      <c r="B23" s="57"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59" t="s">
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="59" t="s">
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K23" s="59"/>
-      <c r="L23" s="59"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
       <c r="O23" s="28"/>
       <c r="P23" s="28"/>
       <c r="Q23" s="28"/>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="19" t="s">
         <v>50</v>
       </c>
@@ -12816,7 +12795,7 @@
       <c r="P24" s="7"/>
       <c r="Q24" s="7"/>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="19">
         <v>1</v>
       </c>
@@ -12857,7 +12836,7 @@
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D26" s="19">
         <v>2</v>
       </c>
@@ -12889,7 +12868,7 @@
       <c r="P26" s="7"/>
       <c r="Q26" s="7"/>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D27" s="19">
         <v>3</v>
       </c>
@@ -12921,7 +12900,7 @@
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D28" s="19"/>
       <c r="E28" s="10"/>
       <c r="F28" s="19"/>
@@ -12947,7 +12926,7 @@
       <c r="P28" s="7"/>
       <c r="Q28" s="7"/>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>
       <c r="G29" s="19">
@@ -12972,7 +12951,7 @@
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D30" s="10"/>
       <c r="E30" s="10"/>
       <c r="G30" s="19">
@@ -12997,7 +12976,7 @@
       <c r="P30" s="7"/>
       <c r="Q30" s="7"/>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
       <c r="G31" s="19">
@@ -13022,7 +13001,7 @@
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
     </row>
-    <row r="32" spans="1:17">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
       <c r="G32" s="19"/>
@@ -13041,7 +13020,7 @@
       <c r="P32" s="7"/>
       <c r="Q32" s="7"/>
     </row>
-    <row r="33" spans="1:17">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
       <c r="G33" s="10"/>
@@ -13060,7 +13039,7 @@
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
     </row>
-    <row r="34" spans="1:17">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
       <c r="G34" s="10"/>
@@ -13079,7 +13058,7 @@
       <c r="P34" s="7"/>
       <c r="Q34" s="7"/>
     </row>
-    <row r="35" spans="1:17">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
       <c r="G35" s="10"/>
@@ -13098,7 +13077,7 @@
       <c r="P35" s="7"/>
       <c r="Q35" s="7"/>
     </row>
-    <row r="36" spans="1:17">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
       <c r="G36" s="10"/>
@@ -13117,7 +13096,7 @@
       <c r="P36" s="7"/>
       <c r="Q36" s="7"/>
     </row>
-    <row r="37" spans="1:17">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
       <c r="G37" s="10"/>
@@ -13136,7 +13115,7 @@
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
     </row>
-    <row r="38" spans="1:17">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
       <c r="G38" s="10"/>
@@ -13155,7 +13134,7 @@
       <c r="P38" s="7"/>
       <c r="Q38" s="7"/>
     </row>
-    <row r="39" spans="1:17">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
       <c r="G39" s="10"/>
@@ -13174,7 +13153,7 @@
       <c r="P39" s="7"/>
       <c r="Q39" s="7"/>
     </row>
-    <row r="40" spans="1:17">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D40" s="10"/>
       <c r="E40" s="10"/>
       <c r="G40" s="10"/>
@@ -13187,48 +13166,48 @@
       <c r="P40" s="7"/>
       <c r="Q40" s="7"/>
     </row>
-    <row r="41" spans="1:17" s="26" customFormat="1" ht="26.25">
-      <c r="A41" s="74" t="s">
+    <row r="41" spans="1:17" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A41" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="74"/>
-      <c r="C41" s="74"/>
-      <c r="D41" s="74"/>
-      <c r="E41" s="74"/>
-      <c r="F41" s="74"/>
-      <c r="G41" s="74"/>
-      <c r="H41" s="74"/>
-      <c r="I41" s="74"/>
-      <c r="J41" s="74"/>
-      <c r="K41" s="74"/>
-      <c r="L41" s="74"/>
+      <c r="B41" s="72"/>
+      <c r="C41" s="72"/>
+      <c r="D41" s="72"/>
+      <c r="E41" s="72"/>
+      <c r="F41" s="72"/>
+      <c r="G41" s="72"/>
+      <c r="H41" s="72"/>
+      <c r="I41" s="72"/>
+      <c r="J41" s="72"/>
+      <c r="K41" s="72"/>
+      <c r="L41" s="72"/>
       <c r="O41" s="28"/>
       <c r="P41" s="28"/>
       <c r="Q41" s="28"/>
     </row>
-    <row r="42" spans="1:17" s="26" customFormat="1" ht="26.25">
-      <c r="A42" s="59" t="s">
+    <row r="42" spans="1:17" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A42" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="59"/>
-      <c r="C42" s="59"/>
-      <c r="D42" s="59" t="s">
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="59"/>
-      <c r="F42" s="59"/>
-      <c r="G42" s="59" t="s">
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H42" s="59"/>
-      <c r="I42" s="59"/>
-      <c r="J42" s="59" t="s">
+      <c r="H42" s="57"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K42" s="59"/>
-      <c r="L42" s="59"/>
-    </row>
-    <row r="43" spans="1:17">
+      <c r="K42" s="57"/>
+      <c r="L42" s="57"/>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
         <v>50</v>
       </c>
@@ -13266,7 +13245,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:17">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="19">
         <v>1</v>
       </c>
@@ -13304,7 +13283,7 @@
         <v>5.6689999999999996</v>
       </c>
     </row>
-    <row r="45" spans="1:17">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D45" s="19">
         <v>2</v>
       </c>
@@ -13333,7 +13312,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:17">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D46" s="19">
         <v>3</v>
       </c>
@@ -13362,7 +13341,7 @@
         <v>12.718999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:17">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D47" s="19"/>
       <c r="E47" s="11"/>
       <c r="F47" s="19"/>
@@ -13385,7 +13364,7 @@
         <v>16.966000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:17">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D48" s="10"/>
       <c r="G48" s="19">
         <v>5</v>
@@ -13406,7 +13385,7 @@
         <v>20.881</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D49" s="10"/>
       <c r="G49" s="19">
         <v>6</v>
@@ -13427,7 +13406,7 @@
         <v>24.969000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D50" s="10"/>
       <c r="G50" s="19">
         <v>7</v>
@@ -13448,7 +13427,7 @@
         <v>28.847999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D51" s="10"/>
       <c r="G51" s="19"/>
       <c r="H51" s="11"/>
@@ -13463,7 +13442,7 @@
         <v>33.03</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D52" s="10"/>
       <c r="G52" s="10"/>
       <c r="H52" s="10"/>
@@ -13478,7 +13457,7 @@
         <v>36.945</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D53" s="10"/>
       <c r="G53" s="10"/>
       <c r="H53" s="10"/>
@@ -13493,7 +13472,7 @@
         <v>40.929000000000002</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D54" s="10"/>
       <c r="G54" s="10"/>
       <c r="H54" s="10"/>
@@ -13508,7 +13487,7 @@
         <v>44.854999999999997</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D55" s="10"/>
       <c r="G55" s="10"/>
       <c r="H55" s="10"/>
@@ -13523,7 +13502,7 @@
         <v>50.978000000000002</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D56" s="10"/>
       <c r="E56" s="10"/>
       <c r="G56" s="10"/>
@@ -13539,7 +13518,7 @@
         <v>66.174999999999997</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D57" s="10"/>
       <c r="E57" s="10"/>
       <c r="G57" s="10"/>
@@ -13555,7 +13534,7 @@
         <v>96.876000000000005</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D58" s="10"/>
       <c r="E58" s="10"/>
       <c r="G58" s="10"/>
@@ -13571,7 +13550,7 @@
         <v>149.39099999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D59" s="10"/>
       <c r="E59" s="10"/>
       <c r="G59" s="10"/>
@@ -13581,45 +13560,45 @@
       <c r="K59" s="24"/>
       <c r="L59" s="25"/>
     </row>
-    <row r="60" spans="1:12" s="26" customFormat="1" ht="26.25">
-      <c r="A60" s="59" t="s">
+    <row r="60" spans="1:12" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A60" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="59"/>
-      <c r="C60" s="59"/>
-      <c r="D60" s="59"/>
-      <c r="E60" s="59"/>
-      <c r="F60" s="59"/>
-      <c r="G60" s="59"/>
-      <c r="H60" s="59"/>
-      <c r="I60" s="59"/>
-      <c r="J60" s="59"/>
-      <c r="K60" s="59"/>
-      <c r="L60" s="59"/>
-    </row>
-    <row r="61" spans="1:12" s="26" customFormat="1" ht="26.25">
-      <c r="A61" s="59" t="s">
+      <c r="B60" s="57"/>
+      <c r="C60" s="57"/>
+      <c r="D60" s="57"/>
+      <c r="E60" s="57"/>
+      <c r="F60" s="57"/>
+      <c r="G60" s="57"/>
+      <c r="H60" s="57"/>
+      <c r="I60" s="57"/>
+      <c r="J60" s="57"/>
+      <c r="K60" s="57"/>
+      <c r="L60" s="57"/>
+    </row>
+    <row r="61" spans="1:12" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A61" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="59"/>
-      <c r="C61" s="59"/>
-      <c r="D61" s="59" t="s">
+      <c r="B61" s="57"/>
+      <c r="C61" s="57"/>
+      <c r="D61" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="59"/>
-      <c r="F61" s="59"/>
-      <c r="G61" s="59" t="s">
+      <c r="E61" s="57"/>
+      <c r="F61" s="57"/>
+      <c r="G61" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H61" s="59"/>
-      <c r="I61" s="59"/>
-      <c r="J61" s="59" t="s">
+      <c r="H61" s="57"/>
+      <c r="I61" s="57"/>
+      <c r="J61" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="59"/>
-      <c r="L61" s="59"/>
-    </row>
-    <row r="62" spans="1:12">
+      <c r="K61" s="57"/>
+      <c r="L61" s="57"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
         <v>50</v>
       </c>
@@ -13657,7 +13636,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="19">
         <v>1</v>
       </c>
@@ -13695,7 +13674,7 @@
         <v>5.6689999999999996</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D64" s="19">
         <v>2</v>
       </c>
@@ -13724,7 +13703,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="4:12">
+    <row r="65" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D65" s="19">
         <v>3</v>
       </c>
@@ -13753,7 +13732,7 @@
         <v>12.718999999999999</v>
       </c>
     </row>
-    <row r="66" spans="4:12">
+    <row r="66" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D66" s="19"/>
       <c r="E66" s="11"/>
       <c r="F66" s="19"/>
@@ -13776,7 +13755,7 @@
         <v>16.966000000000001</v>
       </c>
     </row>
-    <row r="67" spans="4:12">
+    <row r="67" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D67" s="10"/>
       <c r="E67" s="10"/>
       <c r="G67" s="19">
@@ -13798,7 +13777,7 @@
         <v>20.881</v>
       </c>
     </row>
-    <row r="68" spans="4:12">
+    <row r="68" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D68" s="10"/>
       <c r="E68" s="10"/>
       <c r="G68" s="19">
@@ -13820,7 +13799,7 @@
         <v>24.969000000000001</v>
       </c>
     </row>
-    <row r="69" spans="4:12">
+    <row r="69" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D69" s="10"/>
       <c r="E69" s="10"/>
       <c r="G69" s="19">
@@ -13842,7 +13821,7 @@
         <v>28.847999999999999</v>
       </c>
     </row>
-    <row r="70" spans="4:12">
+    <row r="70" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D70" s="10"/>
       <c r="E70" s="10"/>
       <c r="G70" s="19"/>
@@ -13858,7 +13837,7 @@
         <v>33.03</v>
       </c>
     </row>
-    <row r="71" spans="4:12">
+    <row r="71" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D71" s="10"/>
       <c r="E71" s="10"/>
       <c r="G71" s="10"/>
@@ -13874,7 +13853,7 @@
         <v>36.945</v>
       </c>
     </row>
-    <row r="72" spans="4:12">
+    <row r="72" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D72" s="10"/>
       <c r="E72" s="10"/>
       <c r="G72" s="10"/>
@@ -13890,7 +13869,7 @@
         <v>40.929000000000002</v>
       </c>
     </row>
-    <row r="73" spans="4:12">
+    <row r="73" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D73" s="10"/>
       <c r="E73" s="10"/>
       <c r="G73" s="10"/>
@@ -13906,7 +13885,7 @@
         <v>44.854999999999997</v>
       </c>
     </row>
-    <row r="74" spans="4:12">
+    <row r="74" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D74" s="10"/>
       <c r="E74" s="10"/>
       <c r="G74" s="10"/>
@@ -13922,7 +13901,7 @@
         <v>50.978000000000002</v>
       </c>
     </row>
-    <row r="75" spans="4:12">
+    <row r="75" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D75" s="10"/>
       <c r="E75" s="10"/>
       <c r="G75" s="10"/>
@@ -13938,7 +13917,7 @@
         <v>66.174999999999997</v>
       </c>
     </row>
-    <row r="76" spans="4:12">
+    <row r="76" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D76" s="10"/>
       <c r="E76" s="10"/>
       <c r="G76" s="10"/>
@@ -13954,7 +13933,7 @@
         <v>96.876000000000005</v>
       </c>
     </row>
-    <row r="77" spans="4:12">
+    <row r="77" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D77" s="10"/>
       <c r="E77" s="10"/>
       <c r="G77" s="10"/>
@@ -13970,7 +13949,7 @@
         <v>149.39099999999999</v>
       </c>
     </row>
-    <row r="78" spans="4:12">
+    <row r="78" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D78" s="10"/>
       <c r="E78" s="10"/>
       <c r="G78" s="10"/>
